--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G6" t="n">
         <v>2.68</v>
@@ -1888,7 +1888,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
         <v>2.22</v>
@@ -2136,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
         <v>3.25</v>
@@ -2650,7 +2650,7 @@
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>1.69</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>1.78</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
         <v>3.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1.48</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
         <v>8.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
         <v>1.84</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5178,20 +5178,20 @@
         <v>1.96</v>
       </c>
       <c r="G19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.3</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
         <v>6.4</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.6</v>
@@ -5803,7 +5803,7 @@
         <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU21" t="n">
         <v>9.199999999999999</v>
@@ -5815,28 +5815,28 @@
         <v>10.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ21" t="n">
         <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC21" t="n">
         <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF21" t="n">
         <v>4.1</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6191,154 +6191,154 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.52</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N23" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.5</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
         <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
         <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
         <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
         <v>1.03</v>
@@ -6362,7 +6362,7 @@
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6374,13 +6374,13 @@
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6392,13 +6392,13 @@
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6448,19 +6448,19 @@
         <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J24" t="n">
         <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L24" t="n">
         <v>1.44</v>
@@ -6469,16 +6469,16 @@
         <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R24" t="n">
         <v>1.21</v>
@@ -6487,10 +6487,10 @@
         <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V24" t="n">
         <v>1.18</v>
@@ -6499,37 +6499,37 @@
         <v>2.04</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
         <v>140</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
         <v>150</v>
@@ -6538,10 +6538,10 @@
         <v>25</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -6553,46 +6553,46 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
         <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
         <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
         <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
         <v>1.03</v>
@@ -6601,16 +6601,16 @@
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6625,7 +6625,7 @@
         <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,23 +6723,23 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S25" t="n">
         <v>1.39</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T25" t="n">
         <v>1.01</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G26" t="n">
         <v>2.1</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
         <v>4.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>1.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -7718,13 +7718,13 @@
         <v>1.65</v>
       </c>
       <c r="G29" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="H29" t="n">
         <v>6.2</v>
       </c>
       <c r="I29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J29" t="n">
         <v>3.45</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK30" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL30" t="n">
         <v>110</v>
@@ -8158,41 +8158,41 @@
         <v>11</v>
       </c>
       <c r="BQ30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR30" t="n">
         <v>23</v>
       </c>
       <c r="BS30" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU30" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BV30" t="n">
         <v>42</v>
       </c>
       <c r="BW30" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BX30" t="n">
         <v>46</v>
       </c>
       <c r="BY30" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
         <v>16.5</v>
       </c>
       <c r="CA30" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8280,10 +8280,10 @@
         <v>38</v>
       </c>
       <c r="Y31" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA31" t="n">
         <v>260</v>
@@ -8310,7 +8310,7 @@
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ31" t="n">
         <v>16</v>
@@ -8340,7 +8340,7 @@
         <v>4.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -8352,7 +8352,7 @@
         <v>21</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX31" t="n">
         <v>8</v>
@@ -8364,7 +8364,7 @@
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB31" t="n">
         <v>9.6</v>
@@ -8376,13 +8376,13 @@
         <v>20</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF31" t="n">
         <v>3.75</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
         <v>1.83</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -9750,13 +9750,13 @@
         <v>2.32</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="H37" t="n">
         <v>3.25</v>
       </c>
       <c r="I37" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>3.05</v>
@@ -9777,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
         <v>2.24</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
         <v>1.02</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q39" t="n">
         <v>1.02</v>
       </c>
       <c r="R39" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S39" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10363,52 +10363,52 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
         <v>1.02</v>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10533,22 +10533,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P40" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q40" t="n">
         <v>1.41</v>
       </c>
       <c r="R40" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S40" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10617,52 +10617,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
         <v>1.02</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10793,13 +10793,13 @@
         <v>1.02</v>
       </c>
       <c r="P41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R41" t="n">
         <v>1.07</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.06</v>
       </c>
       <c r="S41" t="n">
         <v>1.38</v>
@@ -10871,52 +10871,52 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
         <v>1.02</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11041,22 +11041,22 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P42" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q42" t="n">
         <v>1.02</v>
       </c>
       <c r="R42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S42" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11125,52 +11125,52 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11286,7 @@
         <v>1.02</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11295,19 +11295,19 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O43" t="n">
         <v>1.02</v>
       </c>
       <c r="P43" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q43" t="n">
         <v>1.41</v>
       </c>
       <c r="R43" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S43" t="n">
         <v>1.41</v>
@@ -11379,52 +11379,52 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
         <v>1.02</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P44" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q44" t="n">
         <v>1.02</v>
       </c>
       <c r="R44" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S44" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11633,52 +11633,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G45" t="n">
         <v>2.78</v>
@@ -11794,7 +11794,7 @@
         <v>3.1</v>
       </c>
       <c r="K45" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L45" t="n">
         <v>1.32</v>
@@ -11806,130 +11806,130 @@
         <v>3.45</v>
       </c>
       <c r="O45" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P45" t="n">
         <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R45" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S45" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V45" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W45" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X45" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA45" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI45" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL45" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO45" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
         <v>1.03</v>
@@ -11950,7 +11950,7 @@
         <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
@@ -11962,47 +11962,47 @@
         <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT45" t="n">
         <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
         <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
         <v>1.12</v>
       </c>
       <c r="N46" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O46" t="n">
         <v>1.52</v>
@@ -12078,16 +12078,16 @@
         <v>2.06</v>
       </c>
       <c r="U46" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V46" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
         <v>1.61</v>
       </c>
       <c r="X46" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y46" t="n">
         <v>12</v>
@@ -12102,7 +12102,7 @@
         <v>8.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD46" t="n">
         <v>19.5</v>
@@ -12141,58 +12141,58 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="BF46" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12204,7 +12204,7 @@
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
@@ -12216,13 +12216,13 @@
         <v>1000</v>
       </c>
       <c r="BO46" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP46" t="n">
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
@@ -12234,13 +12234,13 @@
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12311,22 +12311,22 @@
         <v>1.06</v>
       </c>
       <c r="N47" t="n">
-        <v>3.55</v>
+        <v>1.05</v>
       </c>
       <c r="O47" t="n">
         <v>1.3</v>
       </c>
       <c r="P47" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R47" t="n">
         <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T47" t="n">
         <v>1.7</v>
@@ -12335,10 +12335,10 @@
         <v>2.12</v>
       </c>
       <c r="V47" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W47" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X47" t="n">
         <v>18</v>
@@ -12392,61 +12392,61 @@
         <v>40</v>
       </c>
       <c r="AO47" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF47" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BG47" t="n">
-        <v>15</v>
+        <v>3.6</v>
       </c>
       <c r="BH47" t="n">
         <v>3.6</v>
@@ -12458,7 +12458,7 @@
         <v>1000</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
@@ -12470,47 +12470,47 @@
         <v>1000</v>
       </c>
       <c r="BO47" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP47" t="n">
         <v>1000</v>
       </c>
       <c r="BQ47" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR47" t="n">
         <v>1000</v>
       </c>
       <c r="BS47" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT47" t="n">
         <v>1000</v>
       </c>
       <c r="BU47" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV47" t="n">
         <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -12547,25 +12547,25 @@
         <v>2.64</v>
       </c>
       <c r="H48" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I48" t="n">
         <v>3.85</v>
       </c>
       <c r="J48" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K48" t="n">
         <v>3.45</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O48" t="n">
         <v>1.46</v>
@@ -12580,13 +12580,13 @@
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T48" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U48" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V48" t="n">
         <v>1.35</v>
@@ -12604,7 +12604,7 @@
         <v>25</v>
       </c>
       <c r="AA48" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB48" t="n">
         <v>8.6</v>
@@ -12616,7 +12616,7 @@
         <v>16</v>
       </c>
       <c r="AE48" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF48" t="n">
         <v>15.5</v>
@@ -12637,79 +12637,79 @@
         <v>34</v>
       </c>
       <c r="AL48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM48" t="n">
         <v>170</v>
       </c>
       <c r="AN48" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO48" t="n">
         <v>75</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF48" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BG48" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH48" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ48" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK48" t="n">
         <v>1.01</v>
@@ -12721,50 +12721,50 @@
         <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO48" t="n">
         <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ48" t="n">
         <v>1.01</v>
       </c>
       <c r="BR48" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS48" t="n">
         <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU48" t="n">
         <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW48" t="n">
         <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY48" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA48" t="n">
         <v>1.01</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q50" t="n">
         <v>2.16</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
         <v>1.02</v>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -13327,22 +13327,22 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R51" t="n">
         <v>1.07</v>
       </c>
-      <c r="O51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.06</v>
-      </c>
       <c r="S51" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13411,52 +13411,52 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
         <v>1.02</v>
       </c>
       <c r="K52" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13593,7 +13593,7 @@
         <v>1.33</v>
       </c>
       <c r="R52" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S52" t="n">
         <v>1.33</v>
@@ -13665,52 +13665,52 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
         <v>1.02</v>
       </c>
       <c r="K53" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13835,22 +13835,22 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P53" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q53" t="n">
         <v>1.02</v>
       </c>
       <c r="R53" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S53" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -13919,52 +13919,52 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF53" t="n">
         <v>1.01</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
         <v>1.02</v>
       </c>
       <c r="K54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14101,7 +14101,7 @@
         <v>1.36</v>
       </c>
       <c r="R54" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S54" t="n">
         <v>1.36</v>
@@ -14173,52 +14173,52 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
         <v>1.02</v>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14597,22 +14597,22 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P56" t="n">
         <v>1.08</v>
       </c>
-      <c r="O56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R56" t="n">
         <v>1.07</v>
       </c>
-      <c r="Q56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.06</v>
-      </c>
       <c r="S56" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -14681,52 +14681,52 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF56" t="n">
         <v>1.01</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -15344,10 +15344,10 @@
         <v>1.8</v>
       </c>
       <c r="I59" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J59" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K59" t="n">
         <v>950</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>
@@ -15619,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 01:20:12</t>
+          <t>2026-07-10 03:37:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -875,212 +875,212 @@
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
         <v>2.22</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
         <v>2.68</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.38</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
         <v>2.98</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
         <v>1.92</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2.16</v>
@@ -4422,10 +4422,10 @@
         <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q16" t="n">
         <v>1.56</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
         <v>8.4</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K17" t="n">
         <v>5.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
         <v>2.2</v>
@@ -4960,7 +4960,7 @@
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T18" t="n">
         <v>1.84</v>
@@ -4981,22 +4981,22 @@
         <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB18" t="n">
         <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
         <v>13.5</v>
@@ -5008,7 +5008,7 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>30</v>
@@ -5026,7 +5026,7 @@
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -5047,16 +5047,16 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>15.5</v>
@@ -5071,10 +5071,10 @@
         <v>20</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
         <v>14.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
         <v>1.65</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G21" t="n">
         <v>6.6</v>
@@ -5731,7 +5731,7 @@
         <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="W21" t="n">
         <v>1.17</v>
@@ -5764,7 +5764,7 @@
         <v>70</v>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH21" t="n">
         <v>23</v>
@@ -5776,13 +5776,13 @@
         <v>170</v>
       </c>
       <c r="AK21" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="n">
         <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="n">
         <v>70</v>
@@ -5818,19 +5818,19 @@
         <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ21" t="n">
         <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB21" t="n">
         <v>4.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD21" t="n">
         <v>4.2</v>
@@ -5839,10 +5839,10 @@
         <v>4.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH21" t="n">
         <v>4.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6299,58 +6299,58 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6553,58 +6553,58 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH24" t="n">
         <v>2.94</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q25" t="n">
         <v>1.4</v>
@@ -6738,7 +6738,7 @@
         <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -6959,13 +6959,13 @@
         <v>2.1</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
         <v>3.9</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>2.44</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
         <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -7972,13 +7972,13 @@
         <v>1.65</v>
       </c>
       <c r="G30" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H30" t="n">
         <v>5.3</v>
       </c>
       <c r="I30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
         <v>4.2</v>
@@ -8002,7 +8002,7 @@
         <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R30" t="n">
         <v>1.51</v>
@@ -8020,13 +8020,13 @@
         <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X30" t="n">
         <v>23</v>
       </c>
       <c r="Y30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="n">
         <v>55</v>
@@ -8041,7 +8041,7 @@
         <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE30" t="n">
         <v>75</v>
@@ -8071,7 +8071,7 @@
         <v>100</v>
       </c>
       <c r="AN30" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO30" t="n">
         <v>75</v>
@@ -8083,10 +8083,10 @@
         <v>19.5</v>
       </c>
       <c r="AR30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS30" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.9</v>
       </c>
       <c r="AT30" t="n">
         <v>9</v>
@@ -8098,7 +8098,7 @@
         <v>18.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX30" t="n">
         <v>10</v>
@@ -8110,7 +8110,7 @@
         <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB30" t="n">
         <v>15</v>
@@ -8119,16 +8119,16 @@
         <v>14.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH30" t="n">
         <v>4</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
         <v>1.21</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
         <v>6</v>
@@ -8253,25 +8253,25 @@
         <v>1.16</v>
       </c>
       <c r="P31" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R31" t="n">
         <v>1.68</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U31" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W31" t="n">
         <v>3.15</v>
@@ -8280,10 +8280,10 @@
         <v>38</v>
       </c>
       <c r="Y31" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z31" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA31" t="n">
         <v>260</v>
@@ -8334,13 +8334,13 @@
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -8352,7 +8352,7 @@
         <v>21</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX31" t="n">
         <v>8</v>
@@ -8364,7 +8364,7 @@
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB31" t="n">
         <v>9.6</v>
@@ -8376,13 +8376,13 @@
         <v>20</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH31" t="n">
         <v>5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>2.08</v>
       </c>
       <c r="G32" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H32" t="n">
         <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K32" t="n">
         <v>5.4</v>
@@ -8525,10 +8525,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O33" t="n">
         <v>1.24</v>
@@ -8836,7 +8836,7 @@
         <v>13.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP33" t="n">
         <v>16.5</v>
@@ -8845,10 +8845,10 @@
         <v>15</v>
       </c>
       <c r="AR33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AS33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT33" t="n">
         <v>9.199999999999999</v>
@@ -8860,7 +8860,7 @@
         <v>14.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX33" t="n">
         <v>11.5</v>
@@ -8872,7 +8872,7 @@
         <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB33" t="n">
         <v>19</v>
@@ -8881,7 +8881,7 @@
         <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE33" t="n">
         <v>4</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -9248,13 +9248,13 @@
         <v>7.6</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="J35" t="n">
         <v>4.4</v>
       </c>
       <c r="K35" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H36" t="n">
         <v>1.85</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
         <v>2.32</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="H37" t="n">
         <v>3.25</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G39" t="n">
         <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I39" t="n">
         <v>1000</v>
@@ -10270,7 +10270,7 @@
         <v>1.02</v>
       </c>
       <c r="K39" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10509,13 +10509,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G40" t="n">
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I40" t="n">
         <v>1000</v>
@@ -10524,7 +10524,7 @@
         <v>1.02</v>
       </c>
       <c r="K40" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10536,10 +10536,10 @@
         <v>1.09</v>
       </c>
       <c r="O40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P40" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q40" t="n">
         <v>1.41</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G41" t="n">
         <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I41" t="n">
         <v>1000</v>
@@ -10778,7 +10778,7 @@
         <v>1.02</v>
       </c>
       <c r="K41" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10787,13 +10787,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O41" t="n">
         <v>1.02</v>
       </c>
       <c r="P41" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Q41" t="n">
         <v>1.37</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G42" t="n">
         <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I42" t="n">
         <v>1000</v>
@@ -11032,7 +11032,7 @@
         <v>1.02</v>
       </c>
       <c r="K42" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11271,13 +11271,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G43" t="n">
         <v>1000</v>
       </c>
       <c r="H43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
@@ -11286,7 +11286,7 @@
         <v>1.02</v>
       </c>
       <c r="K43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I44" t="n">
         <v>1000</v>
@@ -11540,7 +11540,7 @@
         <v>1.02</v>
       </c>
       <c r="K44" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -11887,58 +11887,58 @@
         <v>38</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12392,58 +12392,58 @@
         <v>40</v>
       </c>
       <c r="AO47" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AP47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR47" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AS47" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV47" t="n">
         <v>3.25</v>
       </c>
-      <c r="AR47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS47" t="n">
+      <c r="AW47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA47" t="n">
         <v>3.9</v>
       </c>
-      <c r="AT47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW47" t="n">
+      <c r="BB47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC47" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX47" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB47" t="n">
+      <c r="BD47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE47" t="n">
         <v>4</v>
       </c>
-      <c r="BC47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF47" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BG47" t="n">
         <v>3.6</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12580,7 @@
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T48" t="n">
         <v>1.96</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.68</v>
       </c>
       <c r="G50" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H50" t="n">
         <v>2.68</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G51" t="n">
         <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I51" t="n">
         <v>1000</v>
@@ -13318,7 +13318,7 @@
         <v>1.02</v>
       </c>
       <c r="K51" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -13336,7 +13336,7 @@
         <v>1.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R51" t="n">
         <v>1.07</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G52" t="n">
         <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I52" t="n">
         <v>1000</v>
@@ -13572,7 +13572,7 @@
         <v>1.02</v>
       </c>
       <c r="K52" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -13811,13 +13811,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G53" t="n">
         <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I53" t="n">
         <v>1000</v>
@@ -13826,7 +13826,7 @@
         <v>1.02</v>
       </c>
       <c r="K53" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13841,7 +13841,7 @@
         <v>1.01</v>
       </c>
       <c r="P53" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q53" t="n">
         <v>1.02</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -14065,13 +14065,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G54" t="n">
         <v>1000</v>
       </c>
       <c r="H54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I54" t="n">
         <v>1000</v>
@@ -14080,7 +14080,7 @@
         <v>1.02</v>
       </c>
       <c r="K54" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G56" t="n">
         <v>1000</v>
       </c>
       <c r="H56" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I56" t="n">
         <v>1000</v>
@@ -14588,7 +14588,7 @@
         <v>1.02</v>
       </c>
       <c r="K56" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14603,10 +14603,10 @@
         <v>1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R56" t="n">
         <v>1.07</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14872,7 @@
         <v>2.06</v>
       </c>
       <c r="U57" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -15341,16 +15341,16 @@
         <v>2.24</v>
       </c>
       <c r="H59" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I59" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J59" t="n">
         <v>3.1</v>
       </c>
       <c r="K59" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>
@@ -15592,16 +15592,16 @@
         <v>2.44</v>
       </c>
       <c r="G60" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H60" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="I60" t="n">
         <v>3.95</v>
       </c>
       <c r="J60" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K60" t="n">
         <v>3.7</v>
@@ -15622,7 +15622,7 @@
         <v>1.54</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 03:37:50</t>
+          <t>2026-07-10 05:55:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
@@ -890,13 +890,13 @@
         <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R2" t="n">
         <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1129,212 +1129,212 @@
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1383,212 +1383,212 @@
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
         <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1619,34 +1619,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
         <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
         <v>1.77</v>
@@ -1655,194 +1655,194 @@
         <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1891,212 +1891,212 @@
         <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2145,212 +2145,212 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
         <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -2399,212 +2399,212 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
         <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2638,227 +2638,227 @@
         <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
         <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
         <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="G10" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.38</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
         <v>2.98</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4673,13 +4673,13 @@
         <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K17" t="n">
         <v>5.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H18" t="n">
         <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
         <v>3.75</v>
@@ -4945,7 +4945,7 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.35</v>
@@ -4954,40 +4954,40 @@
         <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
         <v>3.65</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
@@ -4999,7 +4999,7 @@
         <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
@@ -5014,19 +5014,19 @@
         <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -5035,13 +5035,13 @@
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
@@ -5059,28 +5059,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
         <v>6.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
         <v>14.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
@@ -5104,7 +5104,7 @@
         <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
         <v>16</v>
@@ -5122,7 +5122,7 @@
         <v>7.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV18" t="n">
         <v>36</v>
@@ -5131,20 +5131,20 @@
         <v>7.8</v>
       </c>
       <c r="BX18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA18" t="n">
         <v>7.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.96</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H19" t="n">
         <v>3.9</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="G21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H21" t="n">
         <v>1.51</v>
@@ -5698,7 +5698,7 @@
         <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.21</v>
@@ -5716,7 +5716,7 @@
         <v>2.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
         <v>1.72</v>
@@ -5731,7 +5731,7 @@
         <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="W21" t="n">
         <v>1.17</v>
@@ -5764,7 +5764,7 @@
         <v>70</v>
       </c>
       <c r="AG21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="n">
         <v>23</v>
@@ -5773,19 +5773,19 @@
         <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO21" t="n">
         <v>6.4</v>
@@ -5794,13 +5794,13 @@
         <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
         <v>4</v>
@@ -5809,7 +5809,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
         <v>10.5</v>
@@ -5818,31 +5818,31 @@
         <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.95</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD21" t="n">
         <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="n">
         <v>4.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="K23" t="n">
         <v>3.5</v>
@@ -6212,22 +6212,22 @@
         <v>1.52</v>
       </c>
       <c r="M23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.56</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q23" t="n">
         <v>2.66</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
         <v>3.45</v>
@@ -6239,10 +6239,10 @@
         <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X23" t="n">
         <v>9.4</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H24" t="n">
         <v>4.8</v>
@@ -6460,7 +6460,7 @@
         <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.44</v>
@@ -6472,10 +6472,10 @@
         <v>2.64</v>
       </c>
       <c r="O24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q24" t="n">
         <v>2.4</v>
@@ -6496,7 +6496,7 @@
         <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X24" t="n">
         <v>11.5</v>
@@ -6511,10 +6511,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
         <v>29</v>
@@ -6526,7 +6526,7 @@
         <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
         <v>32</v>
@@ -6535,13 +6535,13 @@
         <v>150</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -6553,58 +6553,58 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AS24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV24" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG24" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH24" t="n">
         <v>2.94</v>
@@ -6616,59 +6616,59 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BN24" t="n">
         <v>4.3</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H25" t="n">
         <v>2.88</v>
@@ -6714,7 +6714,7 @@
         <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6726,19 +6726,19 @@
         <v>1.13</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
         <v>1.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6750,7 +6750,7 @@
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="G26" t="n">
         <v>2.1</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>5.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I27" t="n">
         <v>1.78</v>
@@ -7222,7 +7222,7 @@
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
         <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7757,10 +7757,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -7978,13 +7978,13 @@
         <v>5.3</v>
       </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J30" t="n">
         <v>4.2</v>
       </c>
       <c r="K30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.33</v>
@@ -7996,22 +7996,22 @@
         <v>4.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
         <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
         <v>1.51</v>
       </c>
       <c r="S30" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T30" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U30" t="n">
         <v>2.18</v>
@@ -8113,7 +8113,7 @@
         <v>5.3</v>
       </c>
       <c r="BB30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC30" t="n">
         <v>14.5</v>
@@ -8140,13 +8140,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL30" t="n">
         <v>110</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN30" t="n">
         <v>4.5</v>
@@ -8158,41 +8158,41 @@
         <v>11</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR30" t="n">
         <v>23</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV30" t="n">
         <v>42</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX30" t="n">
         <v>46</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ30" t="n">
         <v>16.5</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8265,13 +8265,13 @@
         <v>2.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W31" t="n">
         <v>3.15</v>
@@ -8310,7 +8310,7 @@
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ31" t="n">
         <v>16</v>
@@ -8331,25 +8331,25 @@
         <v>110</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS31" t="n">
         <v>4.3</v>
       </c>
       <c r="AT31" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="AW31" t="n">
         <v>4.2</v>
@@ -8358,10 +8358,10 @@
         <v>8</v>
       </c>
       <c r="AY31" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>4.1</v>
@@ -8379,7 +8379,7 @@
         <v>4.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BG31" t="n">
         <v>4.2</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G32" t="n">
         <v>2.16</v>
       </c>
       <c r="H32" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I32" t="n">
         <v>3.55</v>
@@ -8492,7 +8492,7 @@
         <v>3.9</v>
       </c>
       <c r="K32" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8504,19 +8504,19 @@
         <v>1.27</v>
       </c>
       <c r="O32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P32" t="n">
         <v>1.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="R32" t="n">
         <v>1.07</v>
       </c>
       <c r="S32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T32" t="n">
         <v>1.03</v>
@@ -8525,7 +8525,7 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
         <v>1.86</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
         <v>2.02</v>
@@ -8743,7 +8743,7 @@
         <v>4.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K33" t="n">
         <v>4.3</v>
@@ -8764,7 +8764,7 @@
         <v>2.16</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R33" t="n">
         <v>1.46</v>
@@ -8785,7 +8785,7 @@
         <v>1.98</v>
       </c>
       <c r="X33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y33" t="n">
         <v>22</v>
@@ -8839,7 +8839,7 @@
         <v>50</v>
       </c>
       <c r="AP33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ33" t="n">
         <v>15</v>
@@ -8881,10 +8881,10 @@
         <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF33" t="n">
         <v>8.199999999999999</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9245,13 +9245,13 @@
         <v>1.44</v>
       </c>
       <c r="H35" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
         <v>13.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K35" t="n">
         <v>5.7</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9496,19 +9496,19 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H36" t="n">
         <v>1.85</v>
       </c>
       <c r="I36" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K36" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>3.25</v>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J37" t="n">
         <v>3.05</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10536,13 +10536,13 @@
         <v>1.09</v>
       </c>
       <c r="O40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P40" t="n">
         <v>1.09</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="R40" t="n">
         <v>1.07</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -10790,13 +10790,13 @@
         <v>1.09</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P41" t="n">
         <v>1.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R41" t="n">
         <v>1.07</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11298,19 +11298,19 @@
         <v>1.09</v>
       </c>
       <c r="O43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R43" t="n">
         <v>1.07</v>
       </c>
       <c r="S43" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -11779,58 +11779,58 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G45" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H45" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I45" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L45" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M45" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P45" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T45" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U45" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V45" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W45" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X45" t="n">
         <v>18.5</v>
@@ -11839,22 +11839,22 @@
         <v>15.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA45" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB45" t="n">
         <v>13.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE45" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF45" t="n">
         <v>21</v>
@@ -11863,10 +11863,10 @@
         <v>14.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ45" t="n">
         <v>44</v>
@@ -11875,79 +11875,79 @@
         <v>34</v>
       </c>
       <c r="AL45" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM45" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO45" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP45" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AR45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT45" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AU45" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AW45" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AX45" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AZ45" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BA45" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BB45" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BC45" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF45" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BG45" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH45" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BJ45" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK45" t="n">
         <v>1.01</v>
@@ -11959,13 +11959,13 @@
         <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO45" t="n">
         <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ45" t="n">
         <v>1.01</v>
@@ -11977,7 +11977,7 @@
         <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G46" t="n">
         <v>2.66</v>
@@ -12054,16 +12054,16 @@
         <v>1.51</v>
       </c>
       <c r="M46" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>1.52</v>
       </c>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q46" t="n">
         <v>2.56</v>
@@ -12078,7 +12078,7 @@
         <v>2.06</v>
       </c>
       <c r="U46" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V46" t="n">
         <v>1.31</v>
@@ -12111,7 +12111,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG46" t="n">
         <v>14.5</v>
@@ -12141,7 +12141,7 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AQ46" t="n">
         <v>3.85</v>
@@ -12150,7 +12150,7 @@
         <v>4.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="AT46" t="n">
         <v>3.4</v>
@@ -12162,19 +12162,19 @@
         <v>4.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="AX46" t="n">
         <v>4.2</v>
       </c>
       <c r="AY46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="BB46" t="n">
         <v>5</v>
@@ -12183,16 +12183,16 @@
         <v>5</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="BF46" t="n">
         <v>5</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12290,13 +12290,13 @@
         <v>2.9</v>
       </c>
       <c r="G47" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="H47" t="n">
         <v>2.32</v>
       </c>
       <c r="I47" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -12317,7 +12317,7 @@
         <v>1.3</v>
       </c>
       <c r="P47" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
         <v>1.81</v>
@@ -12338,7 +12338,7 @@
         <v>1.54</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X47" t="n">
         <v>18</v>
@@ -12356,13 +12356,13 @@
         <v>15.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD47" t="n">
         <v>14.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF47" t="n">
         <v>27</v>
@@ -12395,58 +12395,58 @@
         <v>25</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AR47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV47" t="n">
         <v>3.5</v>
       </c>
-      <c r="AS47" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AW47" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AX47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY47" t="n">
         <v>3.65</v>
       </c>
-      <c r="AY47" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AZ47" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG47" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>3.6</v>
       </c>
       <c r="BH47" t="n">
         <v>3.6</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -12712,59 +12712,59 @@
         <v>11</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BN48" t="n">
         <v>5.3</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP48" t="n">
         <v>22</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BR48" t="n">
         <v>42</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BT48" t="n">
         <v>6.8</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV48" t="n">
         <v>34</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BX48" t="n">
         <v>55</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BZ48" t="n">
         <v>44</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.68</v>
       </c>
       <c r="G50" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H50" t="n">
         <v>2.68</v>
@@ -13079,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q50" t="n">
         <v>2.16</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
         <v>1.07</v>
       </c>
       <c r="S51" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
         <v>1.07</v>
       </c>
       <c r="S52" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
         <v>1.09</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="R54" t="n">
         <v>1.07</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G57" t="n">
         <v>3.6</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>
@@ -15598,13 +15598,13 @@
         <v>3.15</v>
       </c>
       <c r="I60" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>2.9</v>
       </c>
       <c r="K60" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 05:55:17</t>
+          <t>2026-07-10 08:13:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>14.5</v>
@@ -1736,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,25 +1760,25 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -1897,10 +1897,10 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
         <v>1.59</v>
@@ -1936,7 +1936,7 @@
         <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>8.199999999999999</v>
@@ -1951,7 +1951,7 @@
         <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1990,7 +1990,7 @@
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -2014,13 +2014,13 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
         <v>7.6</v>
@@ -2032,7 +2032,7 @@
         <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2184,7 +2184,7 @@
         <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
         <v>32</v>
@@ -2199,31 +2199,31 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
         <v>180</v>
@@ -2241,10 +2241,10 @@
         <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
@@ -2253,10 +2253,10 @@
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -2268,25 +2268,25 @@
         <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF7" t="n">
         <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -2384,25 +2384,25 @@
         <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
         <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
         <v>3.15</v>
@@ -2414,22 +2414,22 @@
         <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
         <v>1.48</v>
@@ -2462,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
@@ -2492,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
@@ -2516,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>2.56</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
@@ -2677,7 +2677,7 @@
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
         <v>40</v>
@@ -2764,7 +2764,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2773,7 +2773,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2785,7 +2785,7 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
         <v>1.03</v>
@@ -2794,7 +2794,7 @@
         <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BH9" t="n">
         <v>4</v>
@@ -2842,7 +2842,7 @@
         <v>44</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2851,14 +2851,14 @@
         <v>21</v>
       </c>
       <c r="BZ9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA9" t="n">
         <v>17.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G13" t="n">
         <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>3.4</v>
@@ -3669,7 +3669,7 @@
         <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -3678,10 +3678,10 @@
         <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
         <v>1.92</v>
@@ -3693,10 +3693,10 @@
         <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
         <v>1.42</v>
@@ -3747,7 +3747,7 @@
         <v>38</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -3765,13 +3765,13 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
         <v>32</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3786,19 +3786,19 @@
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
         <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>28</v>
@@ -3858,7 +3858,7 @@
         <v>26</v>
       </c>
       <c r="BW13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -3911,106 +3911,106 @@
         <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I14" t="n">
         <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
         <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
@@ -4061,22 +4061,22 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,50 +4085,50 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY14" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
         <v>8.4</v>
@@ -4545,7 +4545,7 @@
         <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
         <v>8.6</v>
@@ -4682,7 +4682,7 @@
         <v>5.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4697,10 +4697,10 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R17" t="n">
         <v>1.67</v>
@@ -4709,7 +4709,7 @@
         <v>2.26</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
         <v>2.16</v>
@@ -4736,7 +4736,7 @@
         <v>13.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
         <v>36</v>
@@ -4775,7 +4775,7 @@
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.2</v>
@@ -4784,7 +4784,7 @@
         <v>5.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT17" t="n">
         <v>10.5</v>
@@ -4796,7 +4796,7 @@
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4808,7 +4808,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
@@ -4838,13 +4838,13 @@
         <v>15</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.2</v>
+        <v>2.68</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>21</v>
+        <v>3.25</v>
       </c>
       <c r="BN17" t="n">
         <v>5.9</v>
@@ -4862,35 +4862,35 @@
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>12</v>
+        <v>2.92</v>
       </c>
       <c r="BT17" t="n">
         <v>16</v>
       </c>
       <c r="BU17" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>21</v>
+        <v>3.1</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>21</v>
+        <v>3.1</v>
       </c>
       <c r="BZ17" t="n">
         <v>16</v>
       </c>
       <c r="CA17" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -4939,16 +4939,16 @@
         <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
         <v>1.89</v>
@@ -4957,7 +4957,7 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
         <v>3.6</v>
@@ -4978,10 +4978,10 @@
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
         <v>85</v>
@@ -4993,13 +4993,13 @@
         <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -5008,22 +5008,22 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO18" t="n">
         <v>65</v>
@@ -5038,19 +5038,19 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>8.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
         <v>14</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5062,7 +5062,7 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
         <v>19.5</v>
@@ -5071,16 +5071,16 @@
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
         <v>14.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G19" t="n">
         <v>1.96</v>
@@ -5193,10 +5193,10 @@
         <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
         <v>4.9</v>
@@ -5208,7 +5208,7 @@
         <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R19" t="n">
         <v>1.52</v>
@@ -5232,7 +5232,7 @@
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z19" t="n">
         <v>34</v>
@@ -5253,7 +5253,7 @@
         <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
@@ -5262,19 +5262,19 @@
         <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ19" t="n">
         <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="n">
         <v>10</v>
@@ -5283,13 +5283,13 @@
         <v>36</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS19" t="n">
         <v>65</v>
@@ -5340,19 +5340,19 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="BJ19" t="n">
         <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>1.68</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>21</v>
+        <v>1.93</v>
       </c>
       <c r="BN19" t="n">
         <v>7</v>
@@ -5364,13 +5364,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="BR19" t="n">
         <v>34</v>
       </c>
       <c r="BS19" t="n">
-        <v>14</v>
+        <v>1.83</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
@@ -5382,23 +5382,23 @@
         <v>44</v>
       </c>
       <c r="BW19" t="n">
-        <v>16.5</v>
+        <v>1.85</v>
       </c>
       <c r="BX19" t="n">
         <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>21</v>
+        <v>1.86</v>
       </c>
       <c r="BZ19" t="n">
         <v>25</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.5</v>
+        <v>1.79</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
         <v>1.47</v>
@@ -5785,7 +5785,7 @@
         <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AO21" t="n">
         <v>6.4</v>
@@ -5794,10 +5794,10 @@
         <v>3.95</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
         <v>11</v>
@@ -5824,16 +5824,16 @@
         <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB21" t="n">
         <v>4.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
         <v>4.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -5937,230 +5937,230 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>2.32</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -6239,7 +6239,7 @@
         <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
         <v>1.63</v>
@@ -6356,65 +6356,65 @@
         <v>2.68</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ23" t="n">
         <v>12</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BN23" t="n">
         <v>5.1</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L24" t="n">
         <v>1.44</v>
@@ -6469,22 +6469,22 @@
         <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P24" t="n">
         <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R24" t="n">
         <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T24" t="n">
         <v>2.18</v>
@@ -6514,7 +6514,7 @@
         <v>6.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
         <v>29</v>
@@ -6553,64 +6553,64 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="n">
         <v>3.3</v>
       </c>
       <c r="AV24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG24" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH24" t="n">
         <v>2.94</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
         <v>2.88</v>
@@ -6738,7 +6738,7 @@
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.48</v>
+        <v>1.43</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6750,7 +6750,7 @@
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -7001,7 +7001,7 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
@@ -7061,52 +7061,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -7207,230 +7207,230 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H27" t="n">
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -7461,230 +7461,230 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H28" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="I28" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="J28" t="n">
         <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
         <v>1.58</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -7733,202 +7733,202 @@
         <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
         <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -7987,212 +7987,212 @@
         <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
         <v>1.62</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W30" t="n">
         <v>2.28</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
         <v>1.23</v>
@@ -8259,10 +8259,10 @@
         <v>1.68</v>
       </c>
       <c r="R31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T31" t="n">
         <v>1.74</v>
@@ -8277,10 +8277,10 @@
         <v>2.38</v>
       </c>
       <c r="X31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z31" t="n">
         <v>55</v>
@@ -8292,25 +8292,25 @@
         <v>12</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG31" t="n">
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="n">
         <v>19.5</v>
@@ -8322,7 +8322,7 @@
         <v>36</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN31" t="n">
         <v>9.199999999999999</v>
@@ -8331,58 +8331,58 @@
         <v>75</v>
       </c>
       <c r="AP31" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
         <v>18.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE31" t="n">
         <v>5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
         <v>6.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH31" t="n">
         <v>4</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G32" t="n">
         <v>2.02</v>
@@ -8519,7 +8519,7 @@
         <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U32" t="n">
         <v>2.24</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G33" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H33" t="n">
         <v>7.6</v>
       </c>
       <c r="I33" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
         <v>5.4</v>
@@ -8767,40 +8767,40 @@
         <v>1.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S33" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U33" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
         <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X33" t="n">
         <v>38</v>
       </c>
       <c r="Y33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z33" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="n">
         <v>260</v>
       </c>
       <c r="AB33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC33" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>16.5</v>
       </c>
       <c r="AD33" t="n">
         <v>38</v>
@@ -8809,22 +8809,22 @@
         <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI33" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ33" t="n">
         <v>16</v>
       </c>
       <c r="AK33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL33" t="n">
         <v>34</v>
@@ -8833,22 +8833,22 @@
         <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO33" t="n">
         <v>110</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.95</v>
+        <v>25</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -8857,10 +8857,10 @@
         <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX33" t="n">
         <v>8</v>
@@ -8872,7 +8872,7 @@
         <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB33" t="n">
         <v>9.6</v>
@@ -8884,13 +8884,13 @@
         <v>20</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF33" t="n">
         <v>3.75</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH33" t="n">
         <v>5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>3.55</v>
       </c>
       <c r="J34" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K34" t="n">
         <v>4.7</v>
@@ -9039,112 +9039,112 @@
         <v>1.86</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G36" t="n">
         <v>1.43</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -9753,10 +9753,10 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="I37" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="J37" t="n">
         <v>4.2</v>
@@ -9780,7 +9780,7 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G38" t="n">
         <v>2.6</v>
@@ -10010,7 +10010,7 @@
         <v>3.25</v>
       </c>
       <c r="I38" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>3.05</v>
@@ -10019,40 +10019,40 @@
         <v>3.55</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P38" t="n">
         <v>1.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T38" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U38" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X38" t="n">
         <v>12.5</v>
@@ -10163,68 +10163,68 @@
         <v>4.7</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -11050,13 +11050,13 @@
         <v>1.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -12033,61 +12033,61 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G46" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H46" t="n">
         <v>3.4</v>
       </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="K46" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L46" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M46" t="n">
         <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="O46" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="P46" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S46" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="T46" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U46" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="V46" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W46" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X46" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Y46" t="n">
         <v>12</v>
@@ -12096,167 +12096,167 @@
         <v>29</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB46" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC46" t="n">
         <v>7.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF46" t="n">
         <v>16.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ46" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL46" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN46" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT46" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ46" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AU46" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AV46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX46" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW46" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU46" t="n">
         <v>4.2</v>
       </c>
-      <c r="AZ46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU46" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV46" t="n">
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -12296,10 +12296,10 @@
         <v>2.32</v>
       </c>
       <c r="I47" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K47" t="n">
         <v>3.9</v>
@@ -12311,22 +12311,22 @@
         <v>1.06</v>
       </c>
       <c r="N47" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="O47" t="n">
         <v>1.3</v>
       </c>
       <c r="P47" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R47" t="n">
         <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
         <v>1.7</v>
@@ -12335,7 +12335,7 @@
         <v>2.12</v>
       </c>
       <c r="V47" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W47" t="n">
         <v>1.4</v>
@@ -12356,7 +12356,7 @@
         <v>15.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD47" t="n">
         <v>14.5</v>
@@ -12374,7 +12374,7 @@
         <v>21</v>
       </c>
       <c r="AI47" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ47" t="n">
         <v>65</v>
@@ -12395,58 +12395,58 @@
         <v>25</v>
       </c>
       <c r="AP47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX47" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ47" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV47" t="n">
+      <c r="AY47" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ47" t="n">
         <v>3.5</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="BA47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE47" t="n">
         <v>4</v>
       </c>
-      <c r="AX47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY47" t="n">
+      <c r="BF47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG47" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>3.9</v>
       </c>
       <c r="BH47" t="n">
         <v>3.6</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
         <v>1.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
@@ -12583,7 +12583,7 @@
         <v>3.55</v>
       </c>
       <c r="T48" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U48" t="n">
         <v>1.87</v>
@@ -12595,7 +12595,7 @@
         <v>1.6</v>
       </c>
       <c r="X48" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y48" t="n">
         <v>11.5</v>
@@ -12631,7 +12631,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK48" t="n">
         <v>34</v>
@@ -12649,58 +12649,58 @@
         <v>75</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ48" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AR48" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC48" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS48" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB48" t="n">
+      <c r="BD48" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC48" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD48" t="n">
+      <c r="BE48" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE48" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF48" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG48" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH48" t="n">
         <v>2.98</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H50" t="n">
         <v>2.7</v>
@@ -13073,13 +13073,13 @@
         <v>1.06</v>
       </c>
       <c r="N50" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="O50" t="n">
         <v>1.26</v>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q50" t="n">
         <v>1.78</v>
@@ -13103,10 +13103,10 @@
         <v>1.56</v>
       </c>
       <c r="X50" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z50" t="n">
         <v>25</v>
@@ -13115,7 +13115,7 @@
         <v>55</v>
       </c>
       <c r="AB50" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC50" t="n">
         <v>8.800000000000001</v>
@@ -13127,10 +13127,10 @@
         <v>36</v>
       </c>
       <c r="AF50" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG50" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH50" t="n">
         <v>19.5</v>
@@ -13139,7 +13139,7 @@
         <v>46</v>
       </c>
       <c r="AJ50" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK50" t="n">
         <v>34</v>
@@ -13157,61 +13157,61 @@
         <v>28</v>
       </c>
       <c r="AP50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC50" t="n">
         <v>4</v>
       </c>
-      <c r="AQ50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY50" t="n">
+      <c r="BD50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF50" t="n">
         <v>3.85</v>
       </c>
-      <c r="AZ50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG50" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BH50" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI50" t="n">
         <v>2.94</v>
@@ -13220,59 +13220,59 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BN50" t="n">
         <v>5.9</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP50" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BT50" t="n">
         <v>6.2</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV50" t="n">
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -13835,13 +13835,13 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O53" t="n">
         <v>1.01</v>
       </c>
       <c r="P53" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q53" t="n">
         <v>1.33</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
         <v>1.18</v>
       </c>
       <c r="S55" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G58" t="n">
         <v>3.6</v>
@@ -15099,16 +15099,16 @@
         <v>3.25</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M58" t="n">
         <v>1.12</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P58" t="n">
         <v>1.53</v>
@@ -15117,10 +15117,10 @@
         <v>2.6</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T58" t="n">
         <v>2.08</v>
@@ -15129,182 +15129,182 @@
         <v>1.76</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -15592,16 +15592,16 @@
         <v>1.88</v>
       </c>
       <c r="G60" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="H60" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="I60" t="n">
         <v>6</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K60" t="n">
         <v>3.7</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
         <v>2.78</v>
       </c>
       <c r="H61" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I61" t="n">
         <v>3.7</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-10 10:31:43</t>
+          <t>2026-07-10 12:51:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1392,13 +1392,13 @@
         <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1413,10 +1413,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>4.7</v>
@@ -1820,7 +1820,7 @@
         <v>7.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BV5" t="n">
         <v>30</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -1897,10 +1897,10 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
         <v>1.59</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2145,7 +2145,7 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2154,7 +2154,7 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
         <v>1.66</v>
@@ -2166,7 +2166,7 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
         <v>2.02</v>
@@ -2175,19 +2175,19 @@
         <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
         <v>1.83</v>
       </c>
       <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
         <v>13</v>
       </c>
-      <c r="Y7" t="n">
-        <v>15</v>
-      </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
         <v>120</v>
@@ -2205,16 +2205,16 @@
         <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
         <v>34</v>
@@ -2223,7 +2223,7 @@
         <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>180</v>
@@ -2232,7 +2232,7 @@
         <v>27</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>9.6</v>
@@ -2244,7 +2244,7 @@
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
@@ -2253,10 +2253,10 @@
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -2265,28 +2265,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
         <v>19.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>19</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
         <v>2.72</v>
@@ -2414,25 +2414,25 @@
         <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
         <v>13.5</v>
@@ -2462,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
@@ -2492,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
@@ -2516,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>2.56</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
@@ -2683,7 +2683,7 @@
         <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
         <v>1.64</v>
@@ -2755,7 +2755,7 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>5.7</v>
@@ -2764,7 +2764,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2773,7 +2773,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.65</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H10" t="n">
         <v>4.8</v>
@@ -2907,7 +2907,7 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2940,7 +2940,7 @@
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X10" t="n">
         <v>18</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3170,19 +3170,19 @@
         <v>1.89</v>
       </c>
       <c r="O11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
         <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3308,7 +3308,7 @@
         <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3424,7 +3424,7 @@
         <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
         <v>1.25</v>
@@ -3445,10 +3445,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3651,31 +3651,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
         <v>2.96</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.31</v>
@@ -3693,19 +3693,19 @@
         <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
         <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
@@ -3744,7 +3744,7 @@
         <v>50</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>50</v>
@@ -3753,10 +3753,10 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -3768,7 +3768,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3786,16 +3786,16 @@
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
         <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>19</v>
@@ -3807,13 +3807,13 @@
         <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
         <v>6.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI13" t="n">
         <v>3</v>
@@ -3831,7 +3831,7 @@
         <v>21</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO13" t="n">
         <v>4.7</v>
@@ -3840,7 +3840,7 @@
         <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BR13" t="n">
         <v>34</v>
@@ -3867,14 +3867,14 @@
         <v>21</v>
       </c>
       <c r="BZ13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
         <v>16.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.2</v>
@@ -3929,7 +3929,7 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
@@ -3944,16 +3944,16 @@
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>1.86</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4186,7 +4186,7 @@
         <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
         <v>1.25</v>
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
         <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV16" t="n">
         <v>11.5</v>
@@ -4551,7 +4551,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA16" t="n">
         <v>4.2</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
         <v>8.6</v>
@@ -4703,7 +4703,7 @@
         <v>1.51</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S17" t="n">
         <v>2.26</v>
@@ -4718,7 +4718,7 @@
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
         <v>36</v>
@@ -4766,7 +4766,7 @@
         <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
         <v>5.1</v>
@@ -4778,19 +4778,19 @@
         <v>5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS17" t="n">
         <v>5.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
@@ -4802,10 +4802,10 @@
         <v>9.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
         <v>5.6</v>
@@ -4814,7 +4814,7 @@
         <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
         <v>20</v>
@@ -4826,10 +4826,10 @@
         <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
         <v>3.15</v>
@@ -4838,13 +4838,13 @@
         <v>15</v>
       </c>
       <c r="BK17" t="n">
-        <v>2.68</v>
+        <v>1.78</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="BN17" t="n">
         <v>5.9</v>
@@ -4862,35 +4862,35 @@
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.92</v>
+        <v>1.89</v>
       </c>
       <c r="BT17" t="n">
         <v>16</v>
       </c>
       <c r="BU17" t="n">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="BZ17" t="n">
         <v>16</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -4933,10 +4933,10 @@
         <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.43</v>
@@ -4957,7 +4957,7 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
         <v>3.6</v>
@@ -4978,7 +4978,7 @@
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z18" t="n">
         <v>34</v>
@@ -5008,7 +5008,7 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>30</v>
@@ -5017,7 +5017,7 @@
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>130</v>
@@ -5038,7 +5038,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>8.4</v>
@@ -5062,7 +5062,7 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>19.5</v>
@@ -5071,16 +5071,16 @@
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
         <v>14.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5193,10 +5193,10 @@
         <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>4.9</v>
@@ -5208,7 +5208,7 @@
         <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R19" t="n">
         <v>1.52</v>
@@ -5232,7 +5232,7 @@
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
         <v>34</v>
@@ -5337,68 +5337,68 @@
         <v>25</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP19" t="n">
         <v>13</v>
       </c>
-      <c r="BK19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BN19" t="n">
+      <c r="BQ19" t="n">
         <v>7</v>
       </c>
-      <c r="BO19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BR19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.83</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.85</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.86</v>
+        <v>11</v>
       </c>
       <c r="BZ19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>1.51</v>
       </c>
       <c r="I21" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J21" t="n">
         <v>4.9</v>
@@ -5701,7 +5701,7 @@
         <v>5.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>3.15</v>
@@ -5955,7 +5955,7 @@
         <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -5967,10 +5967,10 @@
         <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -5979,28 +5979,28 @@
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB22" t="n">
         <v>9.6</v>
@@ -6009,10 +6009,10 @@
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF22" t="n">
         <v>17</v>
@@ -6021,28 +6021,28 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ22" t="n">
         <v>42</v>
       </c>
       <c r="AK22" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
         <v>34</v>
       </c>
       <c r="AO22" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP22" t="n">
         <v>9.4</v>
@@ -6081,86 +6081,86 @@
         <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW22" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BX22" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA22" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>50</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6200,31 +6200,31 @@
         <v>3.3</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
@@ -6233,28 +6233,28 @@
         <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
         <v>1.63</v>
       </c>
       <c r="X23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
         <v>29</v>
       </c>
       <c r="AA23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB23" t="n">
         <v>8.4</v>
@@ -6269,16 +6269,16 @@
         <v>75</v>
       </c>
       <c r="AF23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG23" t="n">
         <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
         <v>44</v>
@@ -6287,13 +6287,13 @@
         <v>42</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO23" t="n">
         <v>110</v>
@@ -6305,13 +6305,13 @@
         <v>3.65</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AU23" t="n">
         <v>3.2</v>
@@ -6323,98 +6323,98 @@
         <v>4.9</v>
       </c>
       <c r="AX23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ23" t="n">
         <v>4.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB23" t="n">
         <v>4.7</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF23" t="n">
         <v>4.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH23" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BI23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
         <v>2.26</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>2.22</v>
       </c>
       <c r="BN23" t="n">
         <v>5.1</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.44</v>
@@ -6469,7 +6469,7 @@
         <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
         <v>1.46</v>
@@ -6478,7 +6478,7 @@
         <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R24" t="n">
         <v>1.21</v>
@@ -6610,7 +6610,7 @@
         <v>2.94</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H25" t="n">
         <v>2.88</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O25" t="n">
         <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6750,7 +6750,7 @@
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -6956,10 +6956,10 @@
         <v>1.8</v>
       </c>
       <c r="G26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
         <v>2.3</v>
@@ -6968,7 +6968,7 @@
         <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7004,7 +7004,7 @@
         <v>1.76</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="G27" t="n">
         <v>2.06</v>
@@ -7216,16 +7216,16 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -7246,7 +7246,7 @@
         <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
         <v>1.84</v>
@@ -7255,10 +7255,10 @@
         <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X27" t="n">
         <v>17.5</v>
@@ -7294,13 +7294,13 @@
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
         <v>29</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>46</v>
@@ -7309,7 +7309,7 @@
         <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO27" t="n">
         <v>75</v>
@@ -7321,7 +7321,7 @@
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS27" t="n">
         <v>5.2</v>
@@ -7348,7 +7348,7 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB27" t="n">
         <v>20</v>
@@ -7357,7 +7357,7 @@
         <v>18</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
         <v>5.3</v>
@@ -7366,7 +7366,7 @@
         <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7461,230 +7461,230 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H28" t="n">
         <v>1.72</v>
       </c>
       <c r="I28" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.27</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>2.52</v>
+        <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S28" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
         <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V28" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.14</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.14</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.14</v>
+        <v>10.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.14</v>
+        <v>15.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.14</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.14</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.14</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.14</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.14</v>
+        <v>16.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.14</v>
+        <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.14</v>
+        <v>4.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.14</v>
+        <v>5.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.14</v>
+        <v>5.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>5.1</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BJ28" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BL28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM28" t="n">
         <v>21</v>
       </c>
       <c r="BN28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV28" t="n">
         <v>11.5</v>
       </c>
-      <c r="BO28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>48</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BV28" t="n">
+      <c r="BW28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY28" t="n">
         <v>15.5</v>
       </c>
-      <c r="BW28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>13</v>
-      </c>
       <c r="BZ28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7748,13 +7748,13 @@
         <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R29" t="n">
         <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7823,52 +7823,52 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -7987,13 +7987,13 @@
         <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
@@ -8002,16 +8002,16 @@
         <v>1.62</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U30" t="n">
         <v>1.68</v>
@@ -8023,124 +8023,124 @@
         <v>2.28</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>170</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ30" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BK30" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8149,28 +8149,28 @@
         <v>21</v>
       </c>
       <c r="BN30" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO30" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="BP30" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BQ30" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BT30" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
@@ -8185,14 +8185,14 @@
         <v>21</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA30" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G31" t="n">
         <v>1.72</v>
@@ -8346,7 +8346,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV31" t="n">
         <v>18.5</v>
@@ -8361,7 +8361,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
         <v>4.9</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
         <v>4</v>
       </c>
       <c r="BI32" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ32" t="n">
         <v>9.6</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -8791,13 +8791,13 @@
         <v>42</v>
       </c>
       <c r="Z33" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="n">
         <v>260</v>
       </c>
       <c r="AB33" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC33" t="n">
         <v>14.5</v>
@@ -8839,16 +8839,16 @@
         <v>110</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="AR33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS33" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>5.5</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -8857,13 +8857,13 @@
         <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY33" t="n">
         <v>8.800000000000001</v>
@@ -8872,7 +8872,7 @@
         <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB33" t="n">
         <v>9.6</v>
@@ -8884,13 +8884,13 @@
         <v>20</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF33" t="n">
         <v>3.75</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH33" t="n">
         <v>5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="O34" t="n">
         <v>1.21</v>
@@ -9093,22 +9093,22 @@
         <v>370</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR34" t="n">
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV34" t="n">
         <v>14.5</v>
@@ -9141,10 +9141,10 @@
         <v>26</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BG34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9257,202 +9257,202 @@
         <v>1000</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9508,19 +9508,19 @@
         <v>4.8</v>
       </c>
       <c r="K36" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -9529,194 +9529,194 @@
         <v>1.78</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -9765,16 +9765,16 @@
         <v>4.6</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P37" t="n">
         <v>2.64</v>
@@ -9783,194 +9783,194 @@
         <v>1.44</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G38" t="n">
         <v>2.6</v>
@@ -10010,7 +10010,7 @@
         <v>3.25</v>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J38" t="n">
         <v>3.05</v>
@@ -10169,28 +10169,28 @@
         <v>1.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
@@ -10199,32 +10199,32 @@
         <v>1.01</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11041,22 +11041,22 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O42" t="n">
         <v>1.01</v>
       </c>
       <c r="P42" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12033,13 +12033,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G46" t="n">
         <v>2.6</v>
       </c>
       <c r="H46" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I46" t="n">
         <v>4.1</v>
@@ -12048,13 +12048,13 @@
         <v>2.98</v>
       </c>
       <c r="K46" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L46" t="n">
         <v>1.46</v>
       </c>
       <c r="M46" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N46" t="n">
         <v>2.58</v>
@@ -12072,10 +12072,10 @@
         <v>1.21</v>
       </c>
       <c r="S46" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="T46" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U46" t="n">
         <v>1.83</v>
@@ -12087,10 +12087,10 @@
         <v>1.63</v>
       </c>
       <c r="X46" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z46" t="n">
         <v>29</v>
@@ -12099,7 +12099,7 @@
         <v>90</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC46" t="n">
         <v>7.6</v>
@@ -12141,58 +12141,58 @@
         <v>85</v>
       </c>
       <c r="AP46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>4</v>
       </c>
-      <c r="AQ46" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AR46" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AV46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ46" t="n">
+      <c r="BA46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB46" t="n">
         <v>5.1</v>
       </c>
-      <c r="BA46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG46" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>2.4</v>
       </c>
       <c r="BH46" t="n">
         <v>2.94</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12317,10 +12317,10 @@
         <v>1.3</v>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R47" t="n">
         <v>1.35</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -12574,13 +12574,13 @@
         <v>1.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="T48" t="n">
         <v>1.94</v>
@@ -12598,34 +12598,34 @@
         <v>11.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA48" t="n">
         <v>75</v>
       </c>
       <c r="AB48" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC48" t="n">
         <v>7.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE48" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF48" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG48" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH48" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI48" t="n">
         <v>80</v>
@@ -12649,58 +12649,58 @@
         <v>75</v>
       </c>
       <c r="AP48" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR48" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>6</v>
-      </c>
       <c r="AS48" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="AT48" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="AV48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA48" t="n">
         <v>5.4</v>
       </c>
-      <c r="AW48" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX48" t="n">
+      <c r="BB48" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD48" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="BE48" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF48" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ48" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG48" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH48" t="n">
         <v>2.98</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13049,19 +13049,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G50" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="H50" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="J50" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K50" t="n">
         <v>3.9</v>
@@ -13076,10 +13076,10 @@
         <v>3.45</v>
       </c>
       <c r="O50" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P50" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>1.78</v>
@@ -13091,103 +13091,103 @@
         <v>2.88</v>
       </c>
       <c r="T50" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U50" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V50" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W50" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="X50" t="n">
         <v>21</v>
       </c>
       <c r="Y50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z50" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA50" t="n">
         <v>55</v>
       </c>
       <c r="AB50" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC50" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD50" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF50" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH50" t="n">
         <v>19.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK50" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO50" t="n">
         <v>34</v>
       </c>
-      <c r="AL50" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>28</v>
-      </c>
       <c r="AP50" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR50" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT50" t="n">
         <v>3.55</v>
       </c>
       <c r="AU50" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX50" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AY50" t="n">
         <v>3.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA50" t="n">
         <v>4.2</v>
@@ -13199,19 +13199,19 @@
         <v>4</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE50" t="n">
         <v>4.4</v>
       </c>
       <c r="BF50" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BG50" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH50" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI50" t="n">
         <v>2.94</v>
@@ -13220,7 +13220,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK50" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
@@ -13229,34 +13229,34 @@
         <v>2.82</v>
       </c>
       <c r="BN50" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BO50" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP50" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ50" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BT50" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BU50" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV50" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW50" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
@@ -13268,11 +13268,11 @@
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
         <v>2.48</v>
       </c>
       <c r="I58" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -15105,10 +15105,10 @@
         <v>1.12</v>
       </c>
       <c r="N58" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O58" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P58" t="n">
         <v>1.53</v>
@@ -15120,7 +15120,7 @@
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T58" t="n">
         <v>2.08</v>
@@ -15129,118 +15129,118 @@
         <v>1.76</v>
       </c>
       <c r="V58" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W58" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X58" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA58" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI58" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK58" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL58" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM58" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN58" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO58" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH58" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-10 12:51:41</t>
+          <t>2026-07-10 15:10:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -869,10 +869,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -890,7 +890,7 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -1392,13 +1392,13 @@
         <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G5" t="n">
         <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
         <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
@@ -1643,22 +1643,22 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
         <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>1.84</v>
@@ -1667,13 +1667,13 @@
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>11.5</v>
@@ -1727,16 +1727,16 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,25 +1760,25 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>7.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV5" t="n">
         <v>30</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -1897,7 +1897,7 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
@@ -1930,10 +1930,10 @@
         <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
         <v>75</v>
@@ -1942,7 +1942,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
         <v>15.5</v>
@@ -1957,7 +1957,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>80</v>
@@ -1978,19 +1978,19 @@
         <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2014,25 +2014,25 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -2151,46 +2151,46 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X7" t="n">
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
         <v>7.8</v>
@@ -2199,43 +2199,43 @@
         <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>10.5</v>
@@ -2244,49 +2244,49 @@
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
         <v>7</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="BF7" t="n">
         <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
@@ -2328,7 +2328,7 @@
         <v>7.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV7" t="n">
         <v>40</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -2444,19 +2444,19 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
         <v>21</v>
@@ -2468,31 +2468,31 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
@@ -2501,10 +2501,10 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
@@ -2513,13 +2513,13 @@
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
@@ -2537,10 +2537,10 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
@@ -2647,7 +2647,7 @@
         <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
@@ -2665,28 +2665,28 @@
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2704,7 +2704,7 @@
         <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>18</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
         <v>40</v>
@@ -2737,13 +2737,13 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>60</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>9</v>
@@ -2755,7 +2755,7 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>5.7</v>
@@ -2782,7 +2782,7 @@
         <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2794,7 +2794,7 @@
         <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BH9" t="n">
         <v>4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
@@ -2922,13 +2922,13 @@
         <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
         <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
         <v>1.82</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -3176,13 +3176,13 @@
         <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
         <v>2.64</v>
       </c>
       <c r="H13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>3.35</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>1.39</v>
@@ -3681,16 +3681,16 @@
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
         <v>1.73</v>
@@ -3705,28 +3705,28 @@
         <v>1.61</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
         <v>17</v>
@@ -3738,25 +3738,25 @@
         <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -3765,13 +3765,13 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3780,10 +3780,10 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
@@ -3792,25 +3792,25 @@
         <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="n">
         <v>3.55</v>
@@ -3822,7 +3822,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3837,7 +3837,7 @@
         <v>4.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>14</v>
@@ -3846,13 +3846,13 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
         <v>26</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA13" t="n">
         <v>16.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.2</v>
@@ -3929,28 +3929,28 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.22</v>
@@ -4070,7 +4070,7 @@
         <v>3.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
         <v>3.9</v>
@@ -4434,7 +4434,7 @@
         <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>5.3</v>
@@ -4443,7 +4443,7 @@
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
         <v>1.58</v>
@@ -4452,16 +4452,16 @@
         <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T16" t="n">
         <v>1.55</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
         <v>1.87</v>
@@ -4476,7 +4476,7 @@
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
         <v>16.5</v>
@@ -4485,7 +4485,7 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>38</v>
@@ -4500,7 +4500,7 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
         <v>30</v>
@@ -4527,10 +4527,10 @@
         <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
         <v>11.5</v>
@@ -4542,7 +4542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
         <v>13.5</v>
@@ -4554,7 +4554,7 @@
         <v>12.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4563,10 +4563,10 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
@@ -4599,7 +4599,7 @@
         <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ16" t="n">
         <v>8.199999999999999</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -4691,34 +4691,34 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
         <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R17" t="n">
         <v>1.68</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
         <v>36</v>
@@ -4775,7 +4775,7 @@
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>4.7</v>
@@ -4790,10 +4790,10 @@
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="AW17" t="n">
         <v>5.1</v>
@@ -4814,7 +4814,7 @@
         <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BD17" t="n">
         <v>20</v>
@@ -4823,7 +4823,7 @@
         <v>5.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
         <v>5.1</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
         <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4954,25 +4954,25 @@
         <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
@@ -4987,7 +4987,7 @@
         <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>8.6</v>
@@ -4999,7 +4999,7 @@
         <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -5038,7 +5038,7 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>8.4</v>
@@ -5047,22 +5047,22 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>19.5</v>
@@ -5071,43 +5071,43 @@
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
         <v>14.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ18" t="n">
         <v>6.2</v>
@@ -5116,35 +5116,35 @@
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW18" t="n">
         <v>7.8</v>
       </c>
       <c r="BX18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA18" t="n">
         <v>7.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -5199,7 +5199,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.22</v>
@@ -5208,25 +5208,25 @@
         <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R19" t="n">
         <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
@@ -5250,10 +5250,10 @@
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
@@ -5265,34 +5265,34 @@
         <v>48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
         <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AO19" t="n">
         <v>38</v>
       </c>
       <c r="AP19" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ19" t="n">
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -5313,7 +5313,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>40</v>
@@ -5334,7 +5334,7 @@
         <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -5689,16 +5689,16 @@
         <v>7.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I21" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J21" t="n">
         <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.21</v>
@@ -5716,22 +5716,22 @@
         <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S21" t="n">
         <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
         <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="W21" t="n">
         <v>1.16</v>
@@ -5791,7 +5791,7 @@
         <v>6.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.6</v>
@@ -5803,7 +5803,7 @@
         <v>11</v>
       </c>
       <c r="AT21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU21" t="n">
         <v>9.199999999999999</v>
@@ -5821,13 +5821,13 @@
         <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA21" t="n">
         <v>4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC21" t="n">
         <v>4.3</v>
@@ -5869,7 +5869,7 @@
         <v>6</v>
       </c>
       <c r="BP21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
         <v>11.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
         <v>1.43</v>
@@ -5970,7 +5970,7 @@
         <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -5979,10 +5979,10 @@
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
         <v>1.42</v>
@@ -6102,7 +6102,7 @@
         <v>3.15</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>2.66</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
         <v>3.85</v>
@@ -6221,7 +6221,7 @@
         <v>1.55</v>
       </c>
       <c r="P23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q23" t="n">
         <v>2.62</v>
@@ -6236,7 +6236,7 @@
         <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
         <v>1.35</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
         <v>6.6</v>
@@ -6463,7 +6463,7 @@
         <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
         <v>1.11</v>
@@ -6472,7 +6472,7 @@
         <v>2.64</v>
       </c>
       <c r="O24" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P24" t="n">
         <v>1.58</v>
@@ -6481,34 +6481,34 @@
         <v>2.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U24" t="n">
         <v>1.71</v>
       </c>
       <c r="V24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="X24" t="n">
         <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB24" t="n">
         <v>6.8</v>
@@ -6517,13 +6517,13 @@
         <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
@@ -6532,7 +6532,7 @@
         <v>32</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ24" t="n">
         <v>24</v>
@@ -6544,70 +6544,70 @@
         <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="n">
         <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH24" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI24" t="n">
         <v>2.46</v>
@@ -6616,59 +6616,59 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.96</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.09</v>
+        <v>1.88</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
         <v>1.33</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
         <v>1.33</v>
@@ -6738,7 +6738,7 @@
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -6959,13 +6959,13 @@
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I26" t="n">
         <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -7207,16 +7207,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H27" t="n">
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>3.7</v>
@@ -7225,7 +7225,7 @@
         <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -7237,25 +7237,25 @@
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U27" t="n">
         <v>2.04</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
         <v>1.96</v>
@@ -7276,7 +7276,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
         <v>21</v>
@@ -7321,10 +7321,10 @@
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT27" t="n">
         <v>7.8</v>
@@ -7336,13 +7336,13 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
         <v>16.5</v>
@@ -7357,13 +7357,13 @@
         <v>18</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG27" t="n">
         <v>5.2</v>
@@ -7378,7 +7378,7 @@
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7390,19 +7390,19 @@
         <v>4.9</v>
       </c>
       <c r="BO27" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP27" t="n">
         <v>15</v>
       </c>
       <c r="BQ27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR27" t="n">
         <v>30</v>
       </c>
       <c r="BS27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BT27" t="n">
         <v>8</v>
@@ -7426,11 +7426,11 @@
         <v>27</v>
       </c>
       <c r="CA27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>4.9</v>
       </c>
       <c r="G28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H28" t="n">
         <v>1.7</v>
@@ -7482,7 +7482,7 @@
         <v>1.27</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
         <v>5.4</v>
@@ -7494,25 +7494,25 @@
         <v>2.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R28" t="n">
         <v>1.6</v>
       </c>
       <c r="S28" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
         <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
         <v>2.36</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
         <v>27</v>
@@ -7545,7 +7545,7 @@
         <v>20</v>
       </c>
       <c r="AH28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI28" t="n">
         <v>27</v>
@@ -7563,7 +7563,7 @@
         <v>75</v>
       </c>
       <c r="AN28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO28" t="n">
         <v>7.6</v>
@@ -7587,7 +7587,7 @@
         <v>9.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
@@ -7623,10 +7623,10 @@
         <v>6.6</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ28" t="n">
         <v>9.6</v>
@@ -7641,7 +7641,7 @@
         <v>21</v>
       </c>
       <c r="BN28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO28" t="n">
         <v>7.2</v>
@@ -7680,11 +7680,11 @@
         <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G30" t="n">
         <v>1.72</v>
       </c>
       <c r="H30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
         <v>5.8</v>
@@ -7987,7 +7987,7 @@
         <v>4.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -8002,22 +8002,22 @@
         <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
         <v>2.74</v>
       </c>
       <c r="T30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U30" t="n">
         <v>2.18</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W30" t="n">
         <v>2.38</v>
@@ -8026,7 +8026,7 @@
         <v>24</v>
       </c>
       <c r="Y30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="n">
         <v>55</v>
@@ -8047,7 +8047,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -8059,19 +8059,19 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
         <v>19</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
         <v>75</v>
@@ -8083,10 +8083,10 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT30" t="n">
         <v>9.199999999999999</v>
@@ -8098,7 +8098,7 @@
         <v>18.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
@@ -8110,7 +8110,7 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB30" t="n">
         <v>12.5</v>
@@ -8119,22 +8119,22 @@
         <v>12.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF30" t="n">
         <v>6.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ30" t="n">
         <v>9.800000000000001</v>
@@ -8155,19 +8155,19 @@
         <v>3.6</v>
       </c>
       <c r="BP30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR30" t="n">
         <v>23</v>
       </c>
       <c r="BS30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT30" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>9</v>
       </c>
       <c r="BU30" t="n">
         <v>5.6</v>
@@ -8176,23 +8176,23 @@
         <v>42</v>
       </c>
       <c r="BW30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX30" t="n">
         <v>46</v>
       </c>
       <c r="BY30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G31" t="n">
         <v>1.78</v>
@@ -8241,7 +8241,7 @@
         <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
         <v>1.1</v>
@@ -8388,10 +8388,10 @@
         <v>3.05</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="BJ31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK31" t="n">
         <v>8.800000000000001</v>
@@ -8403,10 +8403,10 @@
         <v>21</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BP31" t="n">
         <v>13</v>
@@ -8424,7 +8424,7 @@
         <v>10.5</v>
       </c>
       <c r="BU31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
         <v>260</v>
       </c>
       <c r="AB32" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC32" t="n">
         <v>14.5</v>
@@ -8567,10 +8567,10 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL32" t="n">
         <v>34</v>
@@ -8579,22 +8579,22 @@
         <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO32" t="n">
         <v>110</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
@@ -8603,10 +8603,10 @@
         <v>10</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX32" t="n">
         <v>9.199999999999999</v>
@@ -8618,7 +8618,7 @@
         <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB32" t="n">
         <v>9.6</v>
@@ -8630,13 +8630,13 @@
         <v>20</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH32" t="n">
         <v>4.9</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -8755,13 +8755,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
         <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q33" t="n">
         <v>1.21</v>
@@ -8803,10 +8803,10 @@
         <v>21</v>
       </c>
       <c r="AD33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="n">
         <v>36</v>
@@ -8815,43 +8815,43 @@
         <v>17</v>
       </c>
       <c r="AH33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI33" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AJ33" t="n">
         <v>44</v>
       </c>
       <c r="AK33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM33" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AN33" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO33" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR33" t="n">
         <v>21</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU33" t="n">
         <v>6.2</v>
@@ -8887,10 +8887,10 @@
         <v>26</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
         <v>13</v>
       </c>
       <c r="AC34" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
         <v>21</v>
@@ -9099,10 +9099,10 @@
         <v>15</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
         <v>9.199999999999999</v>
@@ -9114,7 +9114,7 @@
         <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -9126,7 +9126,7 @@
         <v>14.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB34" t="n">
         <v>19</v>
@@ -9135,19 +9135,19 @@
         <v>16.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF34" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI34" t="n">
         <v>3.4</v>
@@ -9162,7 +9162,7 @@
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN34" t="n">
         <v>5.1</v>
@@ -9174,13 +9174,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR34" t="n">
         <v>25</v>
       </c>
       <c r="BS34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT34" t="n">
         <v>8</v>
@@ -9189,26 +9189,26 @@
         <v>5.7</v>
       </c>
       <c r="BV34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX34" t="n">
         <v>40</v>
       </c>
       <c r="BY34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O35" t="n">
         <v>1.27</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q35" t="n">
         <v>1.27</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>1.34</v>
       </c>
       <c r="G36" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H36" t="n">
         <v>10.5</v>
@@ -9505,10 +9505,10 @@
         <v>14.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="K36" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9523,7 +9523,7 @@
         <v>1.28</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q36" t="n">
         <v>1.83</v>
@@ -9535,16 +9535,16 @@
         <v>3.1</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U36" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V36" t="n">
         <v>1.07</v>
       </c>
       <c r="W36" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X36" t="n">
         <v>17.5</v>
@@ -9556,10 +9556,10 @@
         <v>130</v>
       </c>
       <c r="AA36" t="n">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC36" t="n">
         <v>14</v>
@@ -9568,10 +9568,10 @@
         <v>50</v>
       </c>
       <c r="AE36" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF36" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG36" t="n">
         <v>12.5</v>
@@ -9583,7 +9583,7 @@
         <v>210</v>
       </c>
       <c r="AJ36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK36" t="n">
         <v>19</v>
@@ -9592,67 +9592,67 @@
         <v>55</v>
       </c>
       <c r="AM36" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN36" t="n">
         <v>7.8</v>
       </c>
       <c r="AO36" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AP36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU36" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY36" t="n">
         <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC36" t="n">
         <v>12.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.1</v>
+        <v>36</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF36" t="n">
         <v>5.9</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH36" t="n">
         <v>4.6</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G37" t="n">
         <v>4.5</v>
@@ -9777,10 +9777,10 @@
         <v>1.17</v>
       </c>
       <c r="P37" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R37" t="n">
         <v>1.67</v>
@@ -9792,7 +9792,7 @@
         <v>1.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V37" t="n">
         <v>2.1</v>
@@ -9855,7 +9855,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="AQ37" t="n">
         <v>11.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
         <v>1.11</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
         <v>1.11</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
         <v>1.05</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S39" t="n">
         <v>1.05</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
@@ -10542,22 +10542,22 @@
         <v>1.66</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R40" t="n">
         <v>1.21</v>
       </c>
       <c r="S40" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T40" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
         <v>1.61</v>
@@ -10566,28 +10566,28 @@
         <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA40" t="n">
         <v>80</v>
       </c>
       <c r="AB40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF40" t="n">
         <v>17</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>17.5</v>
       </c>
       <c r="AG40" t="n">
         <v>13.5</v>
@@ -10614,22 +10614,22 @@
         <v>34</v>
       </c>
       <c r="AO40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP40" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR40" t="n">
         <v>18</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU40" t="n">
         <v>5.8</v>
@@ -10638,10 +10638,10 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY40" t="n">
         <v>9</v>
@@ -10650,25 +10650,25 @@
         <v>15</v>
       </c>
       <c r="BA40" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB40" t="n">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BC40" t="n">
-        <v>23</v>
+        <v>4.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BG40" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -11053,7 +11053,7 @@
         <v>1.03</v>
       </c>
       <c r="R42" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
         <v>1.03</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -11803,13 +11803,13 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q45" t="n">
         <v>1.5</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -12795,22 +12795,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G49" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H49" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I49" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
         <v>1.3</v>
@@ -12840,13 +12840,13 @@
         <v>1.66</v>
       </c>
       <c r="U49" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V49" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W49" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X49" t="n">
         <v>21</v>
@@ -12858,10 +12858,10 @@
         <v>28</v>
       </c>
       <c r="AA49" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB49" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC49" t="n">
         <v>8.800000000000001</v>
@@ -12873,10 +12873,10 @@
         <v>42</v>
       </c>
       <c r="AF49" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG49" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH49" t="n">
         <v>19.5</v>
@@ -12885,10 +12885,10 @@
         <v>50</v>
       </c>
       <c r="AJ49" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK49" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL49" t="n">
         <v>42</v>
@@ -12897,64 +12897,64 @@
         <v>95</v>
       </c>
       <c r="AN49" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO49" t="n">
         <v>34</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY49" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AZ49" t="n">
         <v>4</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="BA49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC49" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC49" t="n">
+      <c r="BD49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF49" t="n">
         <v>4</v>
       </c>
-      <c r="BD49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE49" t="n">
+      <c r="BG49" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH49" t="n">
         <v>3.75</v>
@@ -12975,13 +12975,13 @@
         <v>2.82</v>
       </c>
       <c r="BN49" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO49" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP49" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ49" t="n">
         <v>7.2</v>
@@ -12990,19 +12990,19 @@
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BT49" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU49" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV49" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -13058,10 +13058,10 @@
         <v>2.2</v>
       </c>
       <c r="I50" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="J50" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="K50" t="n">
         <v>3.95</v>
@@ -13088,7 +13088,7 @@
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="T50" t="n">
         <v>1.7</v>
@@ -13097,7 +13097,7 @@
         <v>2.12</v>
       </c>
       <c r="V50" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="W50" t="n">
         <v>1.33</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>2.74</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
         <v>3.4</v>
@@ -13578,16 +13578,16 @@
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="O52" t="n">
         <v>1.45</v>
       </c>
       <c r="P52" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q52" t="n">
         <v>2.34</v>
@@ -13608,7 +13608,7 @@
         <v>1.57</v>
       </c>
       <c r="W52" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X52" t="n">
         <v>11.5</v>
@@ -13665,7 +13665,7 @@
         <v>42</v>
       </c>
       <c r="AP52" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ52" t="n">
         <v>7.6</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -13811,13 +13811,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G53" t="n">
         <v>2.48</v>
       </c>
       <c r="H53" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I53" t="n">
         <v>4.4</v>
@@ -13826,37 +13826,37 @@
         <v>2.96</v>
       </c>
       <c r="K53" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L53" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M53" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="R53" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="T53" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U53" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V53" t="n">
         <v>1.3</v>
@@ -13865,7 +13865,7 @@
         <v>1.68</v>
       </c>
       <c r="X53" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y53" t="n">
         <v>12.5</v>
@@ -13874,10 +13874,10 @@
         <v>29</v>
       </c>
       <c r="AA53" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC53" t="n">
         <v>7.6</v>
@@ -13916,125 +13916,125 @@
         <v>34</v>
       </c>
       <c r="AO53" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR53" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA53" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS53" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW53" t="n">
+      <c r="BB53" t="n">
         <v>5.5</v>
       </c>
-      <c r="AX53" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB53" t="n">
+      <c r="BC53" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC53" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD53" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BF53" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG53" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH53" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BI53" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ53" t="n">
         <v>11.5</v>
       </c>
       <c r="BK53" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BN53" t="n">
         <v>5.1</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP53" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ53" t="n">
-        <v>6.8</v>
+        <v>2.04</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BT53" t="n">
         <v>7.2</v>
       </c>
       <c r="BU53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV53" t="n">
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY53" t="n">
         <v>2.18</v>
       </c>
-      <c r="BX53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY53" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -14065,13 +14065,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G54" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H54" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="I54" t="n">
         <v>3.05</v>
@@ -14101,10 +14101,10 @@
         <v>2.16</v>
       </c>
       <c r="R54" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S54" t="n">
-        <v>2.16</v>
+        <v>3.9</v>
       </c>
       <c r="T54" t="n">
         <v>1.01</v>
@@ -14116,7 +14116,7 @@
         <v>1.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14173,52 +14173,52 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ54" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR54" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS54" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AT54" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU54" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV54" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW54" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX54" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY54" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ54" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA54" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB54" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BC54" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BD54" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE54" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14585,7 @@
         <v>1000</v>
       </c>
       <c r="J56" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K56" t="n">
         <v>1000</v>
@@ -14597,13 +14597,13 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O56" t="n">
         <v>1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q56" t="n">
         <v>1.33</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -15335,16 +15335,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G59" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H59" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J59" t="n">
         <v>4.1</v>
@@ -15359,13 +15359,13 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O59" t="n">
         <v>1.14</v>
       </c>
       <c r="P59" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="n">
         <v>1.42</v>
@@ -15380,13 +15380,13 @@
         <v>1.43</v>
       </c>
       <c r="U59" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V59" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W59" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X59" t="n">
         <v>42</v>
@@ -15437,13 +15437,13 @@
         <v>55</v>
       </c>
       <c r="AN59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO59" t="n">
         <v>15</v>
       </c>
       <c r="AP59" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ59" t="n">
         <v>15</v>
@@ -15452,7 +15452,7 @@
         <v>16.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT59" t="n">
         <v>14.5</v>
@@ -15479,7 +15479,7 @@
         <v>18.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC59" t="n">
         <v>15.5</v>
@@ -15488,7 +15488,7 @@
         <v>17</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF59" t="n">
         <v>7.6</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -15589,230 +15589,230 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P60" t="n">
         <v>1.25</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BH60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ60" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G62" t="n">
         <v>3.6</v>
       </c>
       <c r="H62" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I62" t="n">
         <v>2.7</v>
@@ -16121,7 +16121,7 @@
         <v>1.12</v>
       </c>
       <c r="N62" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O62" t="n">
         <v>1.53</v>
@@ -16151,7 +16151,7 @@
         <v>1.39</v>
       </c>
       <c r="X62" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y62" t="n">
         <v>8.199999999999999</v>
@@ -16163,7 +16163,7 @@
         <v>50</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC62" t="n">
         <v>8.800000000000001</v>
@@ -16265,62 +16265,62 @@
         <v>1.01</v>
       </c>
       <c r="BJ62" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK62" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL62" t="n">
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN62" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO62" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP62" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ62" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BR62" t="n">
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT62" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU62" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV62" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW62" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ62" t="n">
         <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -16351,230 +16351,230 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P63" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BA63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BC63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BG63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BH63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI63" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
         <v>1.9</v>
       </c>
       <c r="H64" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I64" t="n">
         <v>6</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
         <v>2.76</v>
       </c>
       <c r="H65" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I65" t="n">
         <v>3.7</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-10 17:29:25</t>
+          <t>2026-07-10 19:47:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
         <v>3.2</v>
@@ -1631,10 +1631,10 @@
         <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.4</v>
@@ -1682,13 +1682,13 @@
         <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
         <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
@@ -1703,7 +1703,7 @@
         <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1736,7 +1736,7 @@
         <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,61 +1760,61 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BG5" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>1.61</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.83</v>
       </c>
       <c r="BN5" t="n">
         <v>8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>15.5</v>
+        <v>1.74</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BT5" t="n">
         <v>7.6</v>
@@ -1826,23 +1826,23 @@
         <v>30</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>1.73</v>
       </c>
       <c r="BX5" t="n">
         <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BZ5" t="n">
         <v>46</v>
       </c>
       <c r="CA5" t="n">
-        <v>20</v>
+        <v>1.76</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -1933,7 +1933,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
         <v>75</v>
@@ -2020,37 +2020,37 @@
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BJ6" t="n">
         <v>15</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>1.57</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BN6" t="n">
         <v>7</v>
@@ -2062,13 +2062,13 @@
         <v>30</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14</v>
+        <v>1.65</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>21</v>
+        <v>1.7</v>
       </c>
       <c r="BT6" t="n">
         <v>8.6</v>
@@ -2080,23 +2080,23 @@
         <v>44</v>
       </c>
       <c r="BW6" t="n">
-        <v>19</v>
+        <v>1.68</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>21</v>
+        <v>1.71</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>21</v>
+        <v>1.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2151,16 +2151,16 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
@@ -2172,19 +2172,19 @@
         <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X7" t="n">
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>29</v>
@@ -2202,7 +2202,7 @@
         <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -2211,13 +2211,13 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
@@ -2229,13 +2229,13 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
         <v>10.5</v>
@@ -2247,7 +2247,7 @@
         <v>36</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU7" t="n">
         <v>7</v>
@@ -2265,16 +2265,16 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
         <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
         <v>29</v>
@@ -2283,7 +2283,7 @@
         <v>46</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG7" t="n">
         <v>34</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2387,55 +2387,55 @@
         <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
         <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -2444,19 +2444,19 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF8" t="n">
         <v>21</v>
@@ -2468,79 +2468,79 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO8" t="n">
         <v>42</v>
       </c>
-      <c r="AO8" t="n">
-        <v>44</v>
-      </c>
       <c r="AP8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
         <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.2</v>
@@ -2659,7 +2659,7 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
@@ -2683,7 +2683,7 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
         <v>1.65</v>
@@ -2692,22 +2692,22 @@
         <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE9" t="n">
         <v>55</v>
@@ -2716,7 +2716,7 @@
         <v>18.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
@@ -2737,10 +2737,10 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
         <v>9.199999999999999</v>
@@ -2749,10 +2749,10 @@
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2776,28 +2776,28 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
         <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI9" t="n">
         <v>2.6</v>
@@ -2806,31 +2806,31 @@
         <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>21</v>
+        <v>3.3</v>
       </c>
       <c r="BN9" t="n">
         <v>7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="BR9" t="n">
         <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>19</v>
+        <v>3.1</v>
       </c>
       <c r="BT9" t="n">
         <v>9.6</v>
@@ -2839,26 +2839,26 @@
         <v>4.3</v>
       </c>
       <c r="BV9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>44</v>
       </c>
-      <c r="BW9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>46</v>
-      </c>
       <c r="CA9" t="n">
-        <v>17.5</v>
+        <v>3.05</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
@@ -2928,7 +2928,7 @@
         <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.82</v>
@@ -2958,7 +2958,7 @@
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
@@ -2997,55 +2997,55 @@
         <v>80</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
@@ -3060,7 +3060,7 @@
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,25 +3072,25 @@
         <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.3</v>
@@ -3179,10 +3179,10 @@
         <v>1.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3308,65 +3308,65 @@
         <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -3678,13 +3678,13 @@
         <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
         <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
@@ -3693,16 +3693,16 @@
         <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X13" t="n">
         <v>16</v>
@@ -3732,7 +3732,7 @@
         <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
         <v>18</v>
@@ -3768,19 +3768,19 @@
         <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>13.5</v>
@@ -3792,28 +3792,28 @@
         <v>14.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD13" t="n">
         <v>8</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI13" t="n">
         <v>3</v>
@@ -3822,16 +3822,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO13" t="n">
         <v>4.3</v>
@@ -3840,41 +3840,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS13" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV13" t="n">
         <v>26</v>
       </c>
       <c r="BW13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -3905,178 +3905,178 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>2.92</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,50 +4085,50 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4207,7 +4207,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
         <v>3.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.25</v>
@@ -4455,7 +4455,7 @@
         <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
         <v>2.66</v>
@@ -4464,7 +4464,7 @@
         <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
@@ -4491,10 +4491,10 @@
         <v>38</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
@@ -4527,10 +4527,10 @@
         <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
         <v>11.5</v>
@@ -4542,7 +4542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>13.5</v>
@@ -4554,7 +4554,7 @@
         <v>12.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4563,10 +4563,10 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF16" t="n">
         <v>7.4</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
         <v>5.5</v>
@@ -4608,7 +4608,7 @@
         <v>23</v>
       </c>
       <c r="BS16" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
@@ -4620,23 +4620,23 @@
         <v>26</v>
       </c>
       <c r="BW16" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
         <v>16.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
         <v>7.8</v>
@@ -4682,7 +4682,7 @@
         <v>5.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4697,28 +4697,28 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
         <v>2.28</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
         <v>36</v>
@@ -4739,7 +4739,7 @@
         <v>14.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
         <v>120</v>
@@ -4775,28 +4775,28 @@
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4808,25 +4808,25 @@
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
         <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
         <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H18" t="n">
         <v>3.75</v>
@@ -4936,10 +4936,10 @@
         <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4969,7 +4969,7 @@
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
         <v>1.83</v>
@@ -4978,7 +4978,7 @@
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
         <v>32</v>
@@ -4990,7 +4990,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
         <v>16</v>
@@ -5038,10 +5038,10 @@
         <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
@@ -5050,7 +5050,7 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5062,7 +5062,7 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
         <v>19.5</v>
@@ -5071,16 +5071,16 @@
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>14.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
@@ -5092,13 +5092,13 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN18" t="n">
         <v>5</v>
@@ -5116,7 +5116,7 @@
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT18" t="n">
         <v>7.6</v>
@@ -5125,26 +5125,26 @@
         <v>5.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
         <v>46</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G19" t="n">
         <v>1.97</v>
@@ -5184,7 +5184,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -5202,10 +5202,10 @@
         <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
         <v>1.68</v>
@@ -5220,7 +5220,7 @@
         <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
@@ -5250,7 +5250,7 @@
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -5280,7 +5280,7 @@
         <v>11.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP19" t="n">
         <v>7.8</v>
@@ -5289,7 +5289,7 @@
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>65</v>
@@ -5313,7 +5313,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
         <v>40</v>
@@ -5334,7 +5334,7 @@
         <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.02</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5686,10 @@
         <v>6.6</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I21" t="n">
         <v>1.55</v>
@@ -5698,10 +5698,10 @@
         <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
@@ -5719,7 +5719,7 @@
         <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S21" t="n">
         <v>2.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6081,10 +6081,10 @@
         <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
         <v>36</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
         <v>1.51</v>
       </c>
       <c r="M23" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N23" t="n">
         <v>2.52</v>
@@ -6236,7 +6236,7 @@
         <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
         <v>1.35</v>
@@ -6257,7 +6257,7 @@
         <v>95</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
         <v>8.199999999999999</v>
@@ -6299,58 +6299,58 @@
         <v>100</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT23" t="n">
         <v>3.25</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY23" t="n">
         <v>4</v>
       </c>
-      <c r="AY23" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH23" t="n">
         <v>2.7</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>6.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="K24" t="n">
         <v>3.6</v>
@@ -6514,7 +6514,7 @@
         <v>6.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
         <v>27</v>
@@ -6553,58 +6553,58 @@
         <v>200</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="AV24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB24" t="n">
         <v>4.8</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="BC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD24" t="n">
         <v>5.5</v>
       </c>
-      <c r="AX24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB24" t="n">
+      <c r="BE24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH24" t="n">
         <v>2.9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I26" t="n">
         <v>2.3</v>
@@ -7004,7 +7004,7 @@
         <v>1.76</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
         <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -7237,10 +7237,10 @@
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
@@ -7378,13 +7378,13 @@
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
         <v>4.9</v>
@@ -7396,13 +7396,13 @@
         <v>15</v>
       </c>
       <c r="BQ27" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
         <v>30</v>
       </c>
       <c r="BS27" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
         <v>8</v>
@@ -7414,23 +7414,23 @@
         <v>38</v>
       </c>
       <c r="BW27" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
         <v>48</v>
       </c>
       <c r="BY27" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
         <v>27</v>
       </c>
       <c r="CA27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7479,10 +7479,10 @@
         <v>4.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
         <v>5.4</v>
@@ -7632,31 +7632,31 @@
         <v>9.6</v>
       </c>
       <c r="BK28" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
         <v>90</v>
       </c>
       <c r="BM28" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO28" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
         <v>36</v>
       </c>
       <c r="BQ28" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
         <v>38</v>
       </c>
       <c r="BS28" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
         <v>5</v>
@@ -7668,23 +7668,23 @@
         <v>11.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
         <v>22</v>
       </c>
       <c r="BY28" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
         <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
         <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>1.72</v>
       </c>
       <c r="H30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I30" t="n">
         <v>5.8</v>
@@ -7999,7 +7999,7 @@
         <v>1.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
         <v>1.69</v>
@@ -8071,7 +8071,7 @@
         <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="n">
         <v>75</v>
@@ -8083,10 +8083,10 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT30" t="n">
         <v>9.199999999999999</v>
@@ -8098,7 +8098,7 @@
         <v>18.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
@@ -8110,7 +8110,7 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB30" t="n">
         <v>12.5</v>
@@ -8119,16 +8119,16 @@
         <v>12.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF30" t="n">
         <v>6.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH30" t="n">
         <v>4.1</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
         <v>160</v>
       </c>
       <c r="AF31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
         <v>13</v>
@@ -8313,19 +8313,19 @@
         <v>160</v>
       </c>
       <c r="AJ31" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
         <v>260</v>
       </c>
       <c r="AN31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO31" t="n">
         <v>280</v>
@@ -8337,10 +8337,10 @@
         <v>14.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
         <v>5.5</v>
@@ -8352,7 +8352,7 @@
         <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
         <v>7.6</v>
@@ -8364,7 +8364,7 @@
         <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
         <v>14.5</v>
@@ -8373,16 +8373,16 @@
         <v>18.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>13</v>
       </c>
       <c r="BG31" t="n">
-        <v>170</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
         <v>3.05</v>
@@ -8394,13 +8394,13 @@
         <v>13</v>
       </c>
       <c r="BK31" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN31" t="n">
         <v>4.1</v>
@@ -8412,41 +8412,41 @@
         <v>13</v>
       </c>
       <c r="BQ31" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="BR31" t="n">
         <v>36</v>
       </c>
       <c r="BS31" t="n">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT31" t="n">
         <v>10.5</v>
       </c>
       <c r="BU31" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BZ31" t="n">
         <v>32</v>
       </c>
       <c r="CA31" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
         <v>260</v>
       </c>
       <c r="AB32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC32" t="n">
         <v>14.5</v>
@@ -8567,7 +8567,7 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK32" t="n">
         <v>16.5</v>
@@ -8585,16 +8585,16 @@
         <v>110</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
@@ -8603,10 +8603,10 @@
         <v>10</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX32" t="n">
         <v>9.199999999999999</v>
@@ -8618,7 +8618,7 @@
         <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB32" t="n">
         <v>9.6</v>
@@ -8630,7 +8630,7 @@
         <v>20</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF32" t="n">
         <v>4.1</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>2.12</v>
       </c>
       <c r="G33" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H33" t="n">
         <v>3.3</v>
@@ -8755,13 +8755,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="O33" t="n">
         <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q33" t="n">
         <v>1.21</v>
@@ -8782,7 +8782,7 @@
         <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X33" t="n">
         <v>90</v>
@@ -8794,7 +8794,7 @@
         <v>55</v>
       </c>
       <c r="AA33" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB33" t="n">
         <v>46</v>
@@ -8803,10 +8803,10 @@
         <v>21</v>
       </c>
       <c r="AD33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF33" t="n">
         <v>36</v>
@@ -8815,28 +8815,28 @@
         <v>17</v>
       </c>
       <c r="AH33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>42</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>44</v>
       </c>
       <c r="AK33" t="n">
         <v>50</v>
       </c>
       <c r="AL33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM33" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AN33" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO33" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP33" t="n">
         <v>4.8</v>
@@ -8848,7 +8848,7 @@
         <v>21</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AT33" t="n">
         <v>4.9</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
         <v>13</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD34" t="n">
         <v>21</v>
@@ -9099,10 +9099,10 @@
         <v>15</v>
       </c>
       <c r="AR34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS34" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
         <v>9.199999999999999</v>
@@ -9114,7 +9114,7 @@
         <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -9126,7 +9126,7 @@
         <v>14.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB34" t="n">
         <v>19</v>
@@ -9135,16 +9135,16 @@
         <v>16.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF34" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BH34" t="n">
         <v>4</v>
@@ -9168,7 +9168,7 @@
         <v>5.1</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP34" t="n">
         <v>13.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O35" t="n">
         <v>1.27</v>
       </c>
       <c r="P35" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
         <v>1.27</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
         <v>13</v>
       </c>
       <c r="AK36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL36" t="n">
         <v>55</v>
@@ -9595,22 +9595,22 @@
         <v>250</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO36" t="n">
         <v>430</v>
       </c>
       <c r="AP36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT36" t="n">
         <v>5.8</v>
@@ -9622,7 +9622,7 @@
         <v>32</v>
       </c>
       <c r="AW36" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX36" t="n">
         <v>6</v>
@@ -9631,10 +9631,10 @@
         <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB36" t="n">
         <v>9.4</v>
@@ -9646,13 +9646,13 @@
         <v>36</v>
       </c>
       <c r="BE36" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF36" t="n">
         <v>5.9</v>
       </c>
       <c r="BG36" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="n">
         <v>4.6</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="R37" t="n">
         <v>1.67</v>
@@ -9855,7 +9855,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP37" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="AQ37" t="n">
         <v>11.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
         <v>3.25</v>
       </c>
       <c r="I40" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
@@ -10557,7 +10557,7 @@
         <v>1.93</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W40" t="n">
         <v>1.61</v>
@@ -10581,13 +10581,13 @@
         <v>8.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE40" t="n">
         <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG40" t="n">
         <v>13.5</v>
@@ -10599,7 +10599,7 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK40" t="n">
         <v>36</v>
@@ -10620,73 +10620,73 @@
         <v>8.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU40" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
       </c>
       <c r="AY40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ40" t="n">
         <v>15</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF40" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE40" t="n">
+      <c r="BG40" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF40" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH40" t="n">
         <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BJ40" t="n">
         <v>14.5</v>
       </c>
       <c r="BK40" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BN40" t="n">
         <v>6.8</v>
@@ -10698,13 +10698,13 @@
         <v>28</v>
       </c>
       <c r="BQ40" t="n">
-        <v>12</v>
+        <v>1.69</v>
       </c>
       <c r="BR40" t="n">
         <v>50</v>
       </c>
       <c r="BS40" t="n">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BT40" t="n">
         <v>8.800000000000001</v>
@@ -10716,23 +10716,23 @@
         <v>44</v>
       </c>
       <c r="BW40" t="n">
-        <v>19</v>
+        <v>1.73</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BZ40" t="n">
         <v>50</v>
       </c>
       <c r="CA40" t="n">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -10787,22 +10787,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="R41" t="n">
         <v>1.14</v>
       </c>
       <c r="S41" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
         <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12063,10 +12063,10 @@
         <v>1.01</v>
       </c>
       <c r="P46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R46" t="n">
         <v>1.07</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -12320,7 +12320,7 @@
         <v>1.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R47" t="n">
         <v>1.18</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12565,7 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -12828,13 +12828,13 @@
         <v>2.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R49" t="n">
         <v>1.42</v>
       </c>
       <c r="S49" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T49" t="n">
         <v>1.66</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13052,22 +13052,22 @@
         <v>2.86</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="H50" t="n">
         <v>2.2</v>
       </c>
       <c r="I50" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="J50" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>3.95</v>
       </c>
       <c r="L50" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M50" t="n">
         <v>1.06</v>
@@ -13088,7 +13088,7 @@
         <v>1.35</v>
       </c>
       <c r="S50" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T50" t="n">
         <v>1.7</v>
@@ -13097,7 +13097,7 @@
         <v>2.12</v>
       </c>
       <c r="V50" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W50" t="n">
         <v>1.33</v>
@@ -13214,7 +13214,7 @@
         <v>3.65</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="BJ50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13360,10 +13360,10 @@
         <v>11.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA51" t="n">
         <v>75</v>
@@ -13375,25 +13375,25 @@
         <v>7.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE51" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF51" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI51" t="n">
         <v>80</v>
       </c>
       <c r="AJ51" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK51" t="n">
         <v>34</v>
@@ -13411,64 +13411,64 @@
         <v>75</v>
       </c>
       <c r="AP51" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AR51" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY51" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS51" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ51" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF51" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH51" t="n">
         <v>2.98</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="BJ51" t="n">
         <v>11</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
         <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13587,7 +13587,7 @@
         <v>1.45</v>
       </c>
       <c r="P52" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q52" t="n">
         <v>2.34</v>
@@ -13599,7 +13599,7 @@
         <v>4.5</v>
       </c>
       <c r="T52" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U52" t="n">
         <v>1.89</v>
@@ -13626,7 +13626,7 @@
         <v>10.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD52" t="n">
         <v>14.5</v>
@@ -13674,7 +13674,7 @@
         <v>13.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT52" t="n">
         <v>8.6</v>
@@ -13686,7 +13686,7 @@
         <v>10.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX52" t="n">
         <v>17.5</v>
@@ -13698,26 +13698,26 @@
         <v>17</v>
       </c>
       <c r="BA52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG52" t="n">
         <v>6</v>
       </c>
-      <c r="BB52" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH52" t="n">
         <v>1000</v>
       </c>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G56" t="n">
         <v>1000</v>
@@ -14597,22 +14597,22 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O56" t="n">
         <v>1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R56" t="n">
         <v>1.18</v>
       </c>
       <c r="S56" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
         <v>1.18</v>
       </c>
       <c r="S57" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O58" t="n">
         <v>1.01</v>
@@ -15114,7 +15114,7 @@
         <v>1.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="R58" t="n">
         <v>1.18</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -15338,10 +15338,10 @@
         <v>2.38</v>
       </c>
       <c r="G59" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H59" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I59" t="n">
         <v>2.94</v>
@@ -15350,7 +15350,7 @@
         <v>4.1</v>
       </c>
       <c r="K59" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -15386,7 +15386,7 @@
         <v>1.52</v>
       </c>
       <c r="W59" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X59" t="n">
         <v>42</v>
@@ -15425,10 +15425,10 @@
         <v>32</v>
       </c>
       <c r="AJ59" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL59" t="n">
         <v>29</v>
@@ -15437,13 +15437,13 @@
         <v>55</v>
       </c>
       <c r="AN59" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO59" t="n">
         <v>15</v>
       </c>
       <c r="AP59" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ59" t="n">
         <v>15</v>
@@ -15452,7 +15452,7 @@
         <v>16.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT59" t="n">
         <v>14.5</v>
@@ -15479,7 +15479,7 @@
         <v>18.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC59" t="n">
         <v>15.5</v>
@@ -15488,7 +15488,7 @@
         <v>17</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF59" t="n">
         <v>7.6</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -15589,166 +15589,166 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="G60" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="H60" t="n">
         <v>3.25</v>
       </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J60" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="K60" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S60" t="n">
         <v>4.2</v>
       </c>
-      <c r="L60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T60" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U60" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="V60" t="n">
         <v>1.38</v>
       </c>
       <c r="W60" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA60" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB60" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC60" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD60" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE60" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF60" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG60" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH60" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI60" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ60" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM60" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO60" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ60" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR60" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.56</v>
+        <v>6.2</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.56</v>
+        <v>6.8</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.56</v>
+        <v>6.2</v>
       </c>
       <c r="AV60" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.43</v>
+        <v>11.5</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.46</v>
+        <v>16.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.56</v>
+        <v>5.6</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.56</v>
+        <v>6.4</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.56</v>
+        <v>5.6</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16115,7 @@
         <v>3.25</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M62" t="n">
         <v>1.12</v>
@@ -16172,7 +16172,7 @@
         <v>15.5</v>
       </c>
       <c r="AE62" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF62" t="n">
         <v>26</v>
@@ -16214,7 +16214,7 @@
         <v>11</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT62" t="n">
         <v>8</v>
@@ -16226,7 +16226,7 @@
         <v>9.4</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX62" t="n">
         <v>15.5</v>
@@ -16238,89 +16238,89 @@
         <v>17</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF62" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG62" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH62" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI62" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BK62" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BL62" t="n">
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BN62" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS62" t="n">
         <v>9</v>
       </c>
-      <c r="BO62" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP62" t="n">
+      <c r="BT62" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX62" t="n">
         <v>48</v>
       </c>
-      <c r="BQ62" t="n">
-        <v>19</v>
-      </c>
-      <c r="BR62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS62" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT62" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU62" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BV62" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW62" t="n">
-        <v>14</v>
-      </c>
-      <c r="BX62" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY62" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ62" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA62" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -16354,55 +16354,55 @@
         <v>1.87</v>
       </c>
       <c r="G63" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>3.5</v>
       </c>
       <c r="K63" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="L63" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O63" t="n">
         <v>1.32</v>
       </c>
       <c r="P63" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R63" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S63" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V63" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W63" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X63" t="n">
         <v>16.5</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -16605,34 +16605,34 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="G64" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="H64" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K64" t="n">
         <v>3.7</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P64" t="n">
         <v>1.65</v>
@@ -16641,194 +16641,194 @@
         <v>2.28</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO64" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG64" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI64" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ64" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>
@@ -16877,16 +16877,16 @@
         <v>3.35</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P65" t="n">
         <v>1.54</v>
@@ -16895,194 +16895,194 @@
         <v>2.48</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BG65" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI65" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BJ65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-10 19:47:45</t>
+          <t>2026-07-10 22:06:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -1628,19 +1628,19 @@
         <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
         <v>3.25</v>
@@ -1655,13 +1655,13 @@
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
@@ -1736,7 +1736,7 @@
         <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,89 +1760,89 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BH5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT5" t="n">
         <v>5.6</v>
       </c>
-      <c r="BG5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP5" t="n">
+      <c r="BU5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>34</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>46</v>
-      </c>
       <c r="CA5" t="n">
-        <v>1.76</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
         <v>2.64</v>
@@ -1885,19 +1885,19 @@
         <v>3.45</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
@@ -1909,19 +1909,19 @@
         <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.6</v>
@@ -1930,7 +1930,7 @@
         <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
         <v>22</v>
@@ -1939,7 +1939,7 @@
         <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
@@ -1966,7 +1966,7 @@
         <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
@@ -1975,7 +1975,7 @@
         <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
         <v>65</v>
@@ -1990,10 +1990,10 @@
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
@@ -2002,7 +2002,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>13</v>
@@ -2011,92 +2011,92 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
         <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
         <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.47</v>
@@ -2298,13 +2298,13 @@
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
         <v>4.9</v>
@@ -2316,41 +2316,41 @@
         <v>17.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
         <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BT7" t="n">
         <v>7.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
         <v>40</v>
       </c>
       <c r="BW7" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>44</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>38</v>
       </c>
       <c r="CA7" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -2399,31 +2399,31 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
         <v>1.98</v>
@@ -2432,7 +2432,7 @@
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>13.5</v>
@@ -2444,16 +2444,16 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -2474,13 +2474,13 @@
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
         <v>40</v>
@@ -2489,85 +2489,85 @@
         <v>42</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
         <v>5.9</v>
       </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.01</v>
@@ -2579,13 +2579,13 @@
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.7</v>
@@ -2659,19 +2659,19 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
@@ -2692,7 +2692,7 @@
         <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
         <v>29</v>
@@ -2701,7 +2701,7 @@
         <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.8</v>
@@ -2716,7 +2716,7 @@
         <v>18.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
@@ -2737,7 +2737,7 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
@@ -2797,7 +2797,7 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI9" t="n">
         <v>2.6</v>
@@ -2806,13 +2806,13 @@
         <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BN9" t="n">
         <v>7</v>
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BR9" t="n">
         <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BT9" t="n">
         <v>9.6</v>
@@ -2842,7 +2842,7 @@
         <v>42</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -2997,58 +2997,58 @@
         <v>80</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.5</v>
@@ -3060,59 +3060,59 @@
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BN10" t="n">
         <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP10" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BZ10" t="n">
         <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3173,13 +3173,13 @@
         <v>1.3</v>
       </c>
       <c r="P11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
         <v>2.56</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -3663,58 +3663,58 @@
         <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
         <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
         <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
@@ -3726,7 +3726,7 @@
         <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
         <v>17</v>
@@ -3738,16 +3738,16 @@
         <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK13" t="n">
         <v>36</v>
       </c>
-      <c r="AK13" t="n">
-        <v>29</v>
-      </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -3756,7 +3756,7 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -3765,13 +3765,13 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
@@ -3780,31 +3780,31 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
@@ -3813,22 +3813,22 @@
         <v>7.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>5.7</v>
@@ -3840,41 +3840,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
         <v>34</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT13" t="n">
         <v>6.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -3905,20 +3905,20 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.09</v>
       </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="K14" t="n">
         <v>1000</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
         <v>1.48</v>
@@ -3944,7 +3944,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3956,7 +3956,7 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4207,7 +4207,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
         <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>3.95</v>
@@ -4434,25 +4434,25 @@
         <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
         <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
         <v>1.58</v>
@@ -4461,22 +4461,22 @@
         <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
         <v>16.5</v>
@@ -4485,25 +4485,25 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF16" t="n">
         <v>19</v>
       </c>
-      <c r="AE16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
@@ -4512,49 +4512,49 @@
         <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>32</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
         <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4563,34 +4563,34 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
         <v>5</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH16" t="n">
         <v>4.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BJ16" t="n">
         <v>9</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
         <v>5.5</v>
@@ -4599,44 +4599,44 @@
         <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BR16" t="n">
         <v>23</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV16" t="n">
         <v>26</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>16.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H17" t="n">
         <v>7.8</v>
@@ -4682,7 +4682,7 @@
         <v>5.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4691,13 +4691,13 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
         <v>1.51</v>
@@ -4724,7 +4724,7 @@
         <v>36</v>
       </c>
       <c r="Y17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="n">
         <v>90</v>
@@ -4733,37 +4733,37 @@
         <v>260</v>
       </c>
       <c r="AB17" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
         <v>120</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -4772,19 +4772,19 @@
         <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT17" t="n">
         <v>10.5</v>
@@ -4793,10 +4793,10 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4808,89 +4808,89 @@
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="BT17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -4936,10 +4936,10 @@
         <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4951,13 +4951,13 @@
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
         <v>3.6</v>
@@ -4966,7 +4966,7 @@
         <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
@@ -4975,58 +4975,58 @@
         <v>1.83</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
         <v>13.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -5035,10 +5035,10 @@
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT18" t="n">
         <v>8.6</v>
@@ -5050,7 +5050,7 @@
         <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5062,25 +5062,25 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG18" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.6</v>
       </c>
       <c r="BH18" t="n">
         <v>3.45</v>
@@ -5092,19 +5092,19 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
         <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP18" t="n">
         <v>16</v>
@@ -5116,35 +5116,35 @@
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
         <v>7.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
         <v>46</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.94</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
@@ -5199,43 +5199,43 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
         <v>1.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
         <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
         <v>95</v>
@@ -5244,16 +5244,16 @@
         <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
@@ -5277,19 +5277,19 @@
         <v>75</v>
       </c>
       <c r="AN19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
         <v>65</v>
@@ -5298,7 +5298,7 @@
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
         <v>15</v>
@@ -5322,25 +5322,25 @@
         <v>19.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD19" t="n">
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="BF19" t="n">
         <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
         <v>9</v>
@@ -5358,7 +5358,7 @@
         <v>5</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP19" t="n">
         <v>13</v>
@@ -5385,20 +5385,20 @@
         <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY19" t="n">
         <v>11</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.55</v>
@@ -5698,25 +5698,25 @@
         <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R21" t="n">
         <v>1.73</v>
@@ -5725,10 +5725,10 @@
         <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U21" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
         <v>2.84</v>
@@ -5749,7 +5749,7 @@
         <v>18</v>
       </c>
       <c r="AB21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AC21" t="n">
         <v>15</v>
@@ -5761,22 +5761,22 @@
         <v>17.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
         <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL21" t="n">
         <v>75</v>
@@ -5785,64 +5785,64 @@
         <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO21" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
         <v>10.5</v>
       </c>
       <c r="AS21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU21" t="n">
         <v>11</v>
       </c>
-      <c r="AT21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AV21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="n">
         <v>4.8</v>
@@ -5854,16 +5854,16 @@
         <v>9.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BO21" t="n">
         <v>6</v>
@@ -5872,13 +5872,13 @@
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT21" t="n">
         <v>4.6</v>
@@ -5890,23 +5890,23 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX21" t="n">
         <v>19</v>
       </c>
       <c r="BY21" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
         <v>11.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -5937,28 +5937,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G22" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
         <v>3.05</v>
@@ -5967,10 +5967,10 @@
         <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -5979,58 +5979,58 @@
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA22" t="n">
         <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AK22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
@@ -6039,128 +6039,128 @@
         <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP22" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
         <v>2.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="BJ23" t="n">
         <v>11.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -6445,76 +6445,76 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="G24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H24" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="O24" t="n">
         <v>1.48</v>
       </c>
       <c r="P24" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R24" t="n">
         <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U24" t="n">
         <v>1.71</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X24" t="n">
         <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
         <v>48</v>
       </c>
       <c r="AA24" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
         <v>27</v>
@@ -6535,10 +6535,10 @@
         <v>140</v>
       </c>
       <c r="AJ24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
         <v>70</v>
@@ -6547,128 +6547,128 @@
         <v>250</v>
       </c>
       <c r="AN24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO24" t="n">
         <v>200</v>
       </c>
       <c r="AP24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BA24" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH24" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -6959,13 +6959,13 @@
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I26" t="n">
         <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -7210,13 +7210,13 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H27" t="n">
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
         <v>3.7</v>
@@ -7225,7 +7225,7 @@
         <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -7237,40 +7237,40 @@
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
         <v>1.85</v>
       </c>
       <c r="U27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
         <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
         <v>9.199999999999999</v>
@@ -7279,19 +7279,19 @@
         <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG27" t="n">
         <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>75</v>
@@ -7300,16 +7300,16 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
         <v>75</v>
@@ -7318,25 +7318,25 @@
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT27" t="n">
         <v>7.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
@@ -7348,61 +7348,61 @@
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BF27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH27" t="n">
         <v>3.5</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN27" t="n">
         <v>4.9</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP27" t="n">
         <v>15</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR27" t="n">
         <v>30</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT27" t="n">
         <v>8</v>
@@ -7414,23 +7414,23 @@
         <v>38</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX27" t="n">
         <v>48</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ27" t="n">
         <v>27</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -7488,22 +7488,22 @@
         <v>5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q28" t="n">
         <v>1.59</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S28" t="n">
         <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U28" t="n">
         <v>2.38</v>
@@ -7530,7 +7530,7 @@
         <v>25</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>10.5</v>
@@ -7566,7 +7566,7 @@
         <v>44</v>
       </c>
       <c r="AO28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP28" t="n">
         <v>20</v>
@@ -7605,7 +7605,7 @@
         <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC28" t="n">
         <v>46</v>
@@ -7623,68 +7623,68 @@
         <v>6.6</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL28" t="n">
         <v>90</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP28" t="n">
         <v>36</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR28" t="n">
         <v>38</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT28" t="n">
         <v>5</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV28" t="n">
         <v>11.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX28" t="n">
         <v>22</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ28" t="n">
         <v>15</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -7996,13 +7996,13 @@
         <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
         <v>1.51</v>
@@ -8053,7 +8053,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>75</v>
@@ -8068,7 +8068,7 @@
         <v>34</v>
       </c>
       <c r="AM30" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN30" t="n">
         <v>8</v>
@@ -8083,10 +8083,10 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT30" t="n">
         <v>9.199999999999999</v>
@@ -8098,7 +8098,7 @@
         <v>18.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
@@ -8110,7 +8110,7 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB30" t="n">
         <v>12.5</v>
@@ -8119,10 +8119,10 @@
         <v>12.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF30" t="n">
         <v>6.4</v>
@@ -8137,13 +8137,13 @@
         <v>3.3</v>
       </c>
       <c r="BJ30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK30" t="n">
         <v>5.9</v>
       </c>
       <c r="BL30" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
         <v>13</v>
@@ -8158,41 +8158,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR30" t="n">
         <v>23</v>
       </c>
       <c r="BS30" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV30" t="n">
         <v>42</v>
       </c>
       <c r="BW30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX30" t="n">
         <v>46</v>
       </c>
       <c r="BY30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>16</v>
       </c>
       <c r="CA30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
         <v>1.65</v>
       </c>
       <c r="G31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H31" t="n">
         <v>6.2</v>
@@ -8235,7 +8235,7 @@
         <v>7.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
@@ -8253,55 +8253,55 @@
         <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q31" t="n">
         <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
         <v>4.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
         <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="n">
         <v>60</v>
       </c>
       <c r="AA31" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD31" t="n">
         <v>34</v>
       </c>
       <c r="AE31" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
         <v>13</v>
@@ -8310,85 +8310,85 @@
         <v>34</v>
       </c>
       <c r="AI31" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN31" t="n">
         <v>18.5</v>
       </c>
-      <c r="AK31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>16</v>
-      </c>
       <c r="AO31" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP31" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH31" t="n">
         <v>3.05</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="BJ31" t="n">
         <v>13</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -8477,25 +8477,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G32" t="n">
         <v>1.45</v>
       </c>
       <c r="H32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>5.4</v>
       </c>
       <c r="K32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M32" t="n">
         <v>1.02</v>
@@ -8513,7 +8513,7 @@
         <v>1.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S32" t="n">
         <v>2.18</v>
@@ -8528,7 +8528,7 @@
         <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X32" t="n">
         <v>38</v>
@@ -8537,16 +8537,16 @@
         <v>38</v>
       </c>
       <c r="Z32" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AA32" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD32" t="n">
         <v>38</v>
@@ -8555,22 +8555,22 @@
         <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI32" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ32" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AK32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL32" t="n">
         <v>34</v>
@@ -8579,46 +8579,46 @@
         <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AO32" t="n">
         <v>110</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT32" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU32" t="n">
         <v>10</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB32" t="n">
         <v>9.6</v>
@@ -8630,31 +8630,31 @@
         <v>20</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH32" t="n">
         <v>4.9</v>
       </c>
       <c r="BI32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN32" t="n">
         <v>4.5</v>
@@ -8666,41 +8666,41 @@
         <v>8.6</v>
       </c>
       <c r="BQ32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT32" t="n">
         <v>12</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ32" t="n">
         <v>11.5</v>
       </c>
       <c r="CA32" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -8755,13 +8755,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="O33" t="n">
         <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
         <v>1.21</v>
@@ -8815,43 +8815,43 @@
         <v>17</v>
       </c>
       <c r="AH33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI33" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ33" t="n">
         <v>42</v>
       </c>
       <c r="AK33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL33" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM33" t="n">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="AN33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO33" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR33" t="n">
         <v>21</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU33" t="n">
         <v>6.2</v>
@@ -8887,10 +8887,10 @@
         <v>26</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BG33" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G34" t="n">
         <v>2.02</v>
       </c>
       <c r="H34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
         <v>4.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.28</v>
@@ -9009,7 +9009,7 @@
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>1.24</v>
@@ -9054,7 +9054,7 @@
         <v>13</v>
       </c>
       <c r="AC34" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
         <v>21</v>
@@ -9099,10 +9099,10 @@
         <v>15</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
         <v>9.199999999999999</v>
@@ -9114,7 +9114,7 @@
         <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX34" t="n">
         <v>11.5</v>
@@ -9126,7 +9126,7 @@
         <v>14.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB34" t="n">
         <v>19</v>
@@ -9135,16 +9135,16 @@
         <v>16.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF34" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH34" t="n">
         <v>4</v>
@@ -9156,7 +9156,7 @@
         <v>9.6</v>
       </c>
       <c r="BK34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
@@ -9174,13 +9174,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ34" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR34" t="n">
         <v>25</v>
       </c>
       <c r="BS34" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT34" t="n">
         <v>8</v>
@@ -9192,7 +9192,7 @@
         <v>34</v>
       </c>
       <c r="BW34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX34" t="n">
         <v>40</v>
@@ -9201,14 +9201,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ34" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA34" t="n">
         <v>6.8</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O35" t="n">
         <v>1.27</v>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q35" t="n">
         <v>1.27</v>
@@ -9278,7 +9278,7 @@
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
         <v>1.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="R36" t="n">
         <v>1.37</v>
@@ -9547,10 +9547,10 @@
         <v>3.3</v>
       </c>
       <c r="X36" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z36" t="n">
         <v>130</v>
@@ -9601,16 +9601,16 @@
         <v>430</v>
       </c>
       <c r="AP36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR36" t="n">
         <v>6.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT36" t="n">
         <v>5.8</v>
@@ -9619,7 +9619,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="AW36" t="n">
         <v>6.6</v>
@@ -9631,7 +9631,7 @@
         <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA36" t="n">
         <v>6.6</v>
@@ -9649,10 +9649,10 @@
         <v>6.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH36" t="n">
         <v>4.6</v>
@@ -9664,59 +9664,59 @@
         <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN36" t="n">
         <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP36" t="n">
         <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR36" t="n">
         <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT36" t="n">
         <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ36" t="n">
         <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R37" t="n">
         <v>1.67</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -10509,64 +10509,64 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H40" t="n">
         <v>3.25</v>
       </c>
       <c r="I40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="K40" t="n">
         <v>3.55</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="P40" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T40" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U40" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W40" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X40" t="n">
         <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
         <v>28</v>
@@ -10581,13 +10581,13 @@
         <v>8.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE40" t="n">
         <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG40" t="n">
         <v>13.5</v>
@@ -10599,7 +10599,7 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK40" t="n">
         <v>36</v>
@@ -10614,7 +10614,7 @@
         <v>34</v>
       </c>
       <c r="AO40" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP40" t="n">
         <v>8.4</v>
@@ -10623,116 +10623,116 @@
         <v>8.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT40" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX40" t="n">
         <v>11</v>
       </c>
       <c r="AY40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ40" t="n">
         <v>15</v>
       </c>
       <c r="BA40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU40" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BJ40" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BN40" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO40" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP40" t="n">
-        <v>28</v>
-      </c>
-      <c r="BQ40" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BR40" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS40" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BT40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU40" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BV40" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.73</v>
+        <v>8</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.75</v>
+        <v>8.6</v>
       </c>
       <c r="BZ40" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -10787,22 +10787,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O41" t="n">
         <v>1.29</v>
       </c>
       <c r="P41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="R41" t="n">
         <v>1.14</v>
       </c>
       <c r="S41" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -12798,16 +12798,16 @@
         <v>2.22</v>
       </c>
       <c r="G49" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H49" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K49" t="n">
         <v>4</v>
@@ -12825,25 +12825,25 @@
         <v>1.27</v>
       </c>
       <c r="P49" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R49" t="n">
         <v>1.42</v>
       </c>
       <c r="S49" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U49" t="n">
         <v>2.24</v>
       </c>
       <c r="V49" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W49" t="n">
         <v>1.68</v>
@@ -12852,10 +12852,10 @@
         <v>21</v>
       </c>
       <c r="Y49" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA49" t="n">
         <v>70</v>
@@ -12864,31 +12864,31 @@
         <v>14</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE49" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF49" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH49" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ49" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL49" t="n">
         <v>42</v>
@@ -12897,70 +12897,70 @@
         <v>95</v>
       </c>
       <c r="AN49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO49" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP49" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AT49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC49" t="n">
         <v>3.7</v>
       </c>
-      <c r="AU49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV49" t="n">
+      <c r="BD49" t="n">
         <v>3.85</v>
       </c>
-      <c r="AW49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX49" t="n">
+      <c r="BE49" t="n">
         <v>4</v>
       </c>
-      <c r="AY49" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF49" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BH49" t="n">
         <v>3.75</v>
       </c>
       <c r="BI49" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BJ49" t="n">
         <v>9.199999999999999</v>
@@ -12972,7 +12972,7 @@
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>2.82</v>
+        <v>8.4</v>
       </c>
       <c r="BN49" t="n">
         <v>5.5</v>
@@ -12990,7 +12990,7 @@
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="BT49" t="n">
         <v>6.8</v>
@@ -13008,17 +13008,17 @@
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.66</v>
+        <v>7.2</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA49" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.86</v>
       </c>
       <c r="G50" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="H50" t="n">
         <v>2.2</v>
@@ -13061,7 +13061,7 @@
         <v>2.52</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="K50" t="n">
         <v>3.95</v>
@@ -13070,25 +13070,25 @@
         <v>1.33</v>
       </c>
       <c r="M50" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P50" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
         <v>1.74</v>
       </c>
       <c r="R50" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S50" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
         <v>1.7</v>
@@ -13100,7 +13100,7 @@
         <v>1.65</v>
       </c>
       <c r="W50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X50" t="n">
         <v>18.5</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
         <v>1.95</v>
       </c>
       <c r="U52" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V52" t="n">
         <v>1.57</v>
@@ -13653,7 +13653,7 @@
         <v>55</v>
       </c>
       <c r="AL52" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM52" t="n">
         <v>160</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -13814,19 +13814,19 @@
         <v>2.18</v>
       </c>
       <c r="G53" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H53" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K53" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L53" t="n">
         <v>1.48</v>
@@ -13835,7 +13835,7 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O53" t="n">
         <v>1.5</v>
@@ -13844,25 +13844,25 @@
         <v>1.53</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R53" t="n">
         <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="T53" t="n">
         <v>2.04</v>
       </c>
       <c r="U53" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V53" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W53" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X53" t="n">
         <v>10.5</v>
@@ -13871,7 +13871,7 @@
         <v>12.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA53" t="n">
         <v>110</v>
@@ -13880,94 +13880,94 @@
         <v>7.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD53" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE53" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF53" t="n">
         <v>15.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH53" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI53" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ53" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK53" t="n">
         <v>38</v>
       </c>
-      <c r="AK53" t="n">
-        <v>36</v>
-      </c>
       <c r="AL53" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM53" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN53" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO53" t="n">
         <v>110</v>
       </c>
       <c r="AP53" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AR53" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS53" t="n">
         <v>5.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AV53" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AW53" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX53" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AY53" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>4.5</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BA53" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE53" t="n">
         <v>5.3</v>
       </c>
-      <c r="BA53" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BF53" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG53" t="n">
         <v>5.2</v>
@@ -13988,7 +13988,7 @@
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>2.24</v>
+        <v>7.4</v>
       </c>
       <c r="BN53" t="n">
         <v>5.1</v>
@@ -14000,13 +14000,13 @@
         <v>21</v>
       </c>
       <c r="BQ53" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="BT53" t="n">
         <v>7.2</v>
@@ -14018,23 +14018,23 @@
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -14068,28 +14068,28 @@
         <v>2.7</v>
       </c>
       <c r="G54" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I54" t="n">
         <v>3.1</v>
       </c>
-      <c r="H54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>3.05</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3.25</v>
       </c>
       <c r="K54" t="n">
         <v>3.55</v>
       </c>
       <c r="L54" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M54" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
         <v>1.39</v>
@@ -14101,139 +14101,139 @@
         <v>2.16</v>
       </c>
       <c r="R54" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S54" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V54" t="n">
         <v>1.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y54" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA54" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB54" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE54" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF54" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG54" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH54" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI54" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK54" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL54" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM54" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO54" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH54" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ54" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK54" t="n">
         <v>1.01</v>
@@ -14245,13 +14245,13 @@
         <v>1.01</v>
       </c>
       <c r="BN54" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO54" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP54" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ54" t="n">
         <v>1.01</v>
@@ -14263,13 +14263,13 @@
         <v>1.01</v>
       </c>
       <c r="BT54" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV54" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="G56" t="n">
         <v>1000</v>
       </c>
       <c r="H56" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I56" t="n">
         <v>1000</v>
@@ -14597,22 +14597,22 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O56" t="n">
         <v>1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R56" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S56" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14851,7 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="O57" t="n">
         <v>1.01</v>
@@ -14866,7 +14866,7 @@
         <v>1.18</v>
       </c>
       <c r="S57" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -15105,16 +15105,16 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q58" t="n">
         <v>1.27</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1.28</v>
       </c>
       <c r="R58" t="n">
         <v>1.18</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G59" t="n">
         <v>2.46</v>
@@ -15344,13 +15344,13 @@
         <v>2.74</v>
       </c>
       <c r="I59" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J59" t="n">
         <v>4.1</v>
       </c>
       <c r="K59" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -15362,7 +15362,7 @@
         <v>7</v>
       </c>
       <c r="O59" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P59" t="n">
         <v>3</v>
@@ -15371,13 +15371,13 @@
         <v>1.42</v>
       </c>
       <c r="R59" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S59" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T59" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U59" t="n">
         <v>2.98</v>
@@ -15392,28 +15392,28 @@
         <v>42</v>
       </c>
       <c r="Y59" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Z59" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA59" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC59" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD59" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE59" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF59" t="n">
         <v>27</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>26</v>
       </c>
       <c r="AG59" t="n">
         <v>15</v>
@@ -15422,7 +15422,7 @@
         <v>17</v>
       </c>
       <c r="AI59" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ59" t="n">
         <v>40</v>
@@ -15434,64 +15434,64 @@
         <v>29</v>
       </c>
       <c r="AM59" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN59" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AO59" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP59" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AQ59" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR59" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS59" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT59" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU59" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV59" t="n">
         <v>11</v>
       </c>
       <c r="AW59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AX59" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY59" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ59" t="n">
         <v>10</v>
       </c>
-      <c r="AZ59" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BA59" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BC59" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD59" t="n">
         <v>17</v>
       </c>
       <c r="BE59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BF59" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BG59" t="n">
         <v>9.4</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -15592,25 +15592,25 @@
         <v>2.42</v>
       </c>
       <c r="G60" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H60" t="n">
         <v>3.25</v>
       </c>
       <c r="I60" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>3.15</v>
       </c>
       <c r="K60" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N60" t="n">
         <v>3</v>
@@ -15625,7 +15625,7 @@
         <v>2.22</v>
       </c>
       <c r="R60" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S60" t="n">
         <v>4.2</v>
@@ -15637,19 +15637,19 @@
         <v>1.93</v>
       </c>
       <c r="V60" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W60" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X60" t="n">
         <v>12.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z60" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA60" t="n">
         <v>75</v>
@@ -15661,28 +15661,28 @@
         <v>8.4</v>
       </c>
       <c r="AD60" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE60" t="n">
         <v>55</v>
       </c>
       <c r="AF60" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG60" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH60" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI60" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ60" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK60" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL60" t="n">
         <v>60</v>
@@ -15691,7 +15691,7 @@
         <v>150</v>
       </c>
       <c r="AN60" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO60" t="n">
         <v>65</v>
@@ -15700,13 +15700,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ60" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR60" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS60" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT60" t="n">
         <v>6.8</v>
@@ -15715,10 +15715,10 @@
         <v>6.2</v>
       </c>
       <c r="AV60" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW60" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AX60" t="n">
         <v>11.5</v>
@@ -15730,25 +15730,25 @@
         <v>16.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BB60" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BC60" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD60" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BE60" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BF60" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG60" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -16097,16 +16097,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G62" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H62" t="n">
         <v>2.48</v>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="J62" t="n">
         <v>3</v>
@@ -16124,10 +16124,10 @@
         <v>2.56</v>
       </c>
       <c r="O62" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P62" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q62" t="n">
         <v>2.6</v>
@@ -16136,34 +16136,34 @@
         <v>1.18</v>
       </c>
       <c r="S62" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T62" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U62" t="n">
         <v>1.76</v>
       </c>
       <c r="V62" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W62" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X62" t="n">
         <v>10.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z62" t="n">
         <v>18.5</v>
       </c>
       <c r="AA62" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC62" t="n">
         <v>8.800000000000001</v>
@@ -16172,7 +16172,7 @@
         <v>15.5</v>
       </c>
       <c r="AE62" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF62" t="n">
         <v>26</v>
@@ -16187,7 +16187,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK62" t="n">
         <v>65</v>
@@ -16202,7 +16202,7 @@
         <v>90</v>
       </c>
       <c r="AO62" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP62" t="n">
         <v>6.6</v>
@@ -16214,10 +16214,10 @@
         <v>11</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT62" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AU62" t="n">
         <v>5.5</v>
@@ -16226,7 +16226,7 @@
         <v>9.4</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX62" t="n">
         <v>15.5</v>
@@ -16238,25 +16238,25 @@
         <v>17</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH62" t="n">
         <v>2.78</v>
@@ -16280,7 +16280,7 @@
         <v>6.6</v>
       </c>
       <c r="BO62" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP62" t="n">
         <v>34</v>
@@ -16298,7 +16298,7 @@
         <v>5.5</v>
       </c>
       <c r="BU62" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BV62" t="n">
         <v>24</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -16354,16 +16354,16 @@
         <v>1.87</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H63" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K63" t="n">
         <v>3.95</v>
@@ -16372,145 +16372,145 @@
         <v>1.01</v>
       </c>
       <c r="M63" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N63" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P63" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R63" t="n">
         <v>1.33</v>
       </c>
       <c r="S63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T63" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="U63" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V63" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W63" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X63" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y63" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z63" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA63" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB63" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC63" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD63" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE63" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF63" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH63" t="n">
         <v>23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ63" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL63" t="n">
         <v>46</v>
       </c>
       <c r="AM63" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN63" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO63" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.82</v>
+        <v>13.5</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.02</v>
+        <v>5</v>
       </c>
       <c r="AS63" t="n">
-        <v>2.02</v>
+        <v>5.5</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="AV63" t="n">
-        <v>2.02</v>
+        <v>16</v>
       </c>
       <c r="AW63" t="n">
-        <v>2.02</v>
+        <v>5.3</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.86</v>
+        <v>17</v>
       </c>
       <c r="BA63" t="n">
-        <v>2.02</v>
+        <v>5.3</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.88</v>
+        <v>19</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.88</v>
+        <v>18.5</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.94</v>
+        <v>5.1</v>
       </c>
       <c r="BE63" t="n">
-        <v>2.02</v>
+        <v>5.5</v>
       </c>
       <c r="BF63" t="n">
-        <v>2.02</v>
+        <v>11</v>
       </c>
       <c r="BG63" t="n">
-        <v>2.02</v>
+        <v>5.3</v>
       </c>
       <c r="BH63" t="n">
         <v>4.1</v>
@@ -16522,59 +16522,59 @@
         <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BN63" t="n">
         <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BP63" t="n">
         <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BR63" t="n">
         <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BT63" t="n">
         <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BV63" t="n">
         <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BZ63" t="n">
         <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -16605,31 +16605,31 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G64" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="H64" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I64" t="n">
         <v>5.4</v>
       </c>
       <c r="J64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K64" t="n">
         <v>3.7</v>
       </c>
       <c r="L64" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M64" t="n">
         <v>1.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O64" t="n">
         <v>1.43</v>
@@ -16638,13 +16638,13 @@
         <v>1.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R64" t="n">
         <v>1.24</v>
       </c>
       <c r="S64" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T64" t="n">
         <v>2.02</v>
@@ -16656,13 +16656,13 @@
         <v>1.22</v>
       </c>
       <c r="W64" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="X64" t="n">
         <v>12.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z64" t="n">
         <v>44</v>
@@ -16671,7 +16671,7 @@
         <v>160</v>
       </c>
       <c r="AB64" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC64" t="n">
         <v>8</v>
@@ -16680,10 +16680,10 @@
         <v>24</v>
       </c>
       <c r="AE64" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF64" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG64" t="n">
         <v>11</v>
@@ -16707,7 +16707,7 @@
         <v>190</v>
       </c>
       <c r="AN64" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO64" t="n">
         <v>140</v>
@@ -16767,16 +16767,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH64" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="BJ64" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
@@ -16785,28 +16785,28 @@
         <v>1.01</v>
       </c>
       <c r="BN64" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO64" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP64" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT64" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU64" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
@@ -16824,11 +16824,11 @@
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>
@@ -16859,10 +16859,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G65" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H65" t="n">
         <v>3.15</v>
@@ -16892,7 +16892,7 @@
         <v>1.54</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R65" t="n">
         <v>1.19</v>
@@ -16913,28 +16913,28 @@
         <v>1.57</v>
       </c>
       <c r="X65" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z65" t="n">
         <v>30</v>
       </c>
       <c r="AA65" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB65" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC65" t="n">
         <v>7.4</v>
       </c>
       <c r="AD65" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE65" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF65" t="n">
         <v>16</v>
@@ -16946,22 +16946,22 @@
         <v>23</v>
       </c>
       <c r="AI65" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ65" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK65" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL65" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM65" t="n">
         <v>200</v>
       </c>
       <c r="AN65" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO65" t="n">
         <v>80</v>
@@ -16973,10 +16973,10 @@
         <v>8.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AS65" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT65" t="n">
         <v>6.8</v>
@@ -16985,13 +16985,13 @@
         <v>6</v>
       </c>
       <c r="AV65" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX65" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY65" t="n">
         <v>10.5</v>
@@ -17000,25 +17000,25 @@
         <v>18.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB65" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="BC65" t="n">
-        <v>25</v>
+        <v>5.9</v>
       </c>
       <c r="BD65" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BE65" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BF65" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG65" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH65" t="n">
         <v>3.2</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-10 22:06:01</t>
+          <t>2026-07-11 00:24:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB66"/>
+  <dimension ref="A1:CB68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1159,7 +1159,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1628,16 +1628,16 @@
         <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1691,7 +1691,7 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
         <v>36</v>
@@ -1700,7 +1700,7 @@
         <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
         <v>20</v>
@@ -1709,7 +1709,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
         <v>44</v>
@@ -1736,7 +1736,7 @@
         <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1760,25 +1760,25 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BG5" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.8</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1805,7 +1805,7 @@
         <v>5.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ5" t="n">
         <v>9</v>
@@ -1814,7 +1814,7 @@
         <v>55</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
         <v>5.6</v>
@@ -1826,7 +1826,7 @@
         <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>38</v>
@@ -1838,11 +1838,11 @@
         <v>34</v>
       </c>
       <c r="CA5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G6" t="n">
         <v>2.64</v>
@@ -1888,7 +1888,7 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1924,7 +1924,7 @@
         <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X6" t="n">
         <v>9.6</v>
@@ -1999,7 +1999,7 @@
         <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>8.199999999999999</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
         <v>2.4</v>
@@ -2202,7 +2202,7 @@
         <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -2220,7 +2220,7 @@
         <v>29</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
         <v>2.7</v>
@@ -2399,7 +2399,7 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -2420,19 +2420,19 @@
         <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V8" t="n">
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
         <v>13.5</v>
@@ -2453,7 +2453,7 @@
         <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>42</v>
@@ -2474,7 +2474,7 @@
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
@@ -2498,19 +2498,19 @@
         <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -2519,28 +2519,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
         <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="n">
         <v>3.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H9" t="n">
         <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
@@ -2656,7 +2656,7 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
         <v>3.45</v>
@@ -2665,10 +2665,10 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
@@ -2725,13 +2725,13 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
@@ -2740,22 +2740,22 @@
         <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS9" t="n">
         <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
         <v>5.8</v>
@@ -2770,10 +2770,10 @@
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.01</v>
@@ -2782,7 +2782,7 @@
         <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>1.01</v>
@@ -2791,7 +2791,7 @@
         <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
@@ -2806,31 +2806,31 @@
         <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BN9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO9" t="n">
         <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BR9" t="n">
         <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BT9" t="n">
         <v>9.6</v>
@@ -2839,26 +2839,26 @@
         <v>4.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>2.96</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>3</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -2898,13 +2898,13 @@
         <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
@@ -2913,7 +2913,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
         <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.25</v>
@@ -4446,10 +4446,10 @@
         <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
         <v>2.42</v>
@@ -4536,16 +4536,16 @@
         <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -4569,7 +4569,7 @@
         <v>5</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
         <v>18.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
         <v>8.4</v>
@@ -4706,13 +4706,13 @@
         <v>1.7</v>
       </c>
       <c r="S17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.22</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.18</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -4730,7 +4730,7 @@
         <v>90</v>
       </c>
       <c r="AA17" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
         <v>12</v>
@@ -4745,7 +4745,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
@@ -4760,55 +4760,55 @@
         <v>13.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO17" t="n">
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BB17" t="n">
         <v>11.5</v>
@@ -4817,16 +4817,16 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BH17" t="n">
         <v>4.7</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G18" t="n">
         <v>2.18</v>
@@ -4948,10 +4948,10 @@
         <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>1.99</v>
@@ -4963,7 +4963,7 @@
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.08</v>
@@ -5017,7 +5017,7 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
@@ -5038,7 +5038,7 @@
         <v>7.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>8.6</v>
@@ -5047,10 +5047,10 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5062,7 +5062,7 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
@@ -5074,7 +5074,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
@@ -5092,13 +5092,13 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
         <v>5</v>
@@ -5110,41 +5110,41 @@
         <v>16</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU18" t="n">
         <v>6</v>
       </c>
       <c r="BV18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>46</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
         <v>28</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.27</v>
@@ -5208,7 +5208,7 @@
         <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R19" t="n">
         <v>1.54</v>
@@ -5217,7 +5217,7 @@
         <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
         <v>2.42</v>
@@ -5259,7 +5259,7 @@
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
         <v>46</v>
@@ -5280,7 +5280,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
@@ -5328,7 +5328,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BF19" t="n">
         <v>9</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="G21" t="n">
         <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I21" t="n">
         <v>1.54</v>
@@ -5728,7 +5728,7 @@
         <v>1.66</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V21" t="n">
         <v>2.84</v>
@@ -5848,7 +5848,7 @@
         <v>4.8</v>
       </c>
       <c r="BI21" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.6</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -5937,46 +5937,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="G22" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>2.94</v>
+        <v>2.46</v>
       </c>
       <c r="I22" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
         <v>1.44</v>
@@ -5985,10 +5985,10 @@
         <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="X22" t="n">
         <v>970</v>
@@ -5997,7 +5997,7 @@
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -6012,7 +6012,7 @@
         <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
         <v>970</v>
@@ -6024,16 +6024,16 @@
         <v>970</v>
       </c>
       <c r="AI22" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -6078,7 +6078,7 @@
         <v>1.53</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BB22" t="n">
         <v>1.58</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
         <v>3.15</v>
       </c>
       <c r="K23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6221,7 +6221,7 @@
         <v>1.42</v>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
         <v>2.26</v>
@@ -6233,10 +6233,10 @@
         <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
         <v>1.44</v>
@@ -6260,7 +6260,7 @@
         <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD23" t="n">
         <v>16.5</v>
@@ -6308,7 +6308,7 @@
         <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -6320,7 +6320,7 @@
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX23" t="n">
         <v>14</v>
@@ -6332,25 +6332,25 @@
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB23" t="n">
         <v>34</v>
       </c>
       <c r="BC23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF23" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>1.83</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
         <v>6.8</v>
@@ -6723,7 +6723,7 @@
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O25" t="n">
         <v>1.48</v>
@@ -6732,7 +6732,7 @@
         <v>1.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
@@ -6747,10 +6747,10 @@
         <v>1.72</v>
       </c>
       <c r="V25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X25" t="n">
         <v>11.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="G26" t="n">
-        <v>2.72</v>
+        <v>27</v>
       </c>
       <c r="H26" t="n">
         <v>2.88</v>
@@ -6965,10 +6965,10 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6983,28 +6983,28 @@
         <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>1.35</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U26" t="n">
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="I27" t="n">
         <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -7470,10 +7470,10 @@
         <v>4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
         <v>3.9</v>
@@ -7488,13 +7488,13 @@
         <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P28" t="n">
         <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R28" t="n">
         <v>1.34</v>
@@ -7503,16 +7503,16 @@
         <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
         <v>2.06</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X28" t="n">
         <v>15</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L29" t="n">
         <v>1.28</v>
@@ -7745,22 +7745,22 @@
         <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S29" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U29" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V29" t="n">
         <v>2.36</v>
@@ -7826,7 +7826,7 @@
         <v>20</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>11</v>
@@ -7889,13 +7889,13 @@
         <v>4.8</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN29" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>9</v>
       </c>
       <c r="BO29" t="n">
         <v>4.7</v>
@@ -7910,7 +7910,7 @@
         <v>38</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT29" t="n">
         <v>5</v>
@@ -7934,18 +7934,18 @@
         <v>15</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,239 +7960,239 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R30" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>1.38</v>
+        <v>4.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -8226,19 +8226,19 @@
         <v>1.65</v>
       </c>
       <c r="G31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H31" t="n">
         <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.28</v>
@@ -8256,7 +8256,7 @@
         <v>2.34</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
         <v>1.52</v>
@@ -8271,10 +8271,10 @@
         <v>2.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W31" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X31" t="n">
         <v>24</v>
@@ -8301,10 +8301,10 @@
         <v>75</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AH31" t="n">
         <v>22</v>
@@ -8325,10 +8325,10 @@
         <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO31" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP31" t="n">
         <v>18</v>
@@ -8337,10 +8337,10 @@
         <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT31" t="n">
         <v>9.4</v>
@@ -8352,7 +8352,7 @@
         <v>18.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -8364,7 +8364,7 @@
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB31" t="n">
         <v>14.5</v>
@@ -8373,16 +8373,16 @@
         <v>14.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF31" t="n">
         <v>7.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH31" t="n">
         <v>4.1</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,239 +8468,239 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>1.79</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.86</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>4.7</v>
+        <v>1.38</v>
       </c>
       <c r="T32" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
         <v>1.39</v>
       </c>
       <c r="G33" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H33" t="n">
         <v>7.8</v>
@@ -8743,10 +8743,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K33" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
         <v>1.21</v>
@@ -8773,7 +8773,7 @@
         <v>2.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U33" t="n">
         <v>2.18</v>
@@ -8782,7 +8782,7 @@
         <v>1.13</v>
       </c>
       <c r="W33" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X33" t="n">
         <v>38</v>
@@ -8839,13 +8839,13 @@
         <v>110</v>
       </c>
       <c r="AP33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AR33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS33" t="n">
         <v>5.6</v>
@@ -8872,7 +8872,7 @@
         <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB33" t="n">
         <v>11.5</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,246 +8976,246 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tobol Kostanay</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="H34" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR34" t="n">
         <v>4.1</v>
       </c>
-      <c r="J34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X34" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP34" t="n">
+      <c r="AS34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN34" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="BO34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT34" t="n">
         <v>8</v>
       </c>
-      <c r="AR34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA34" t="n">
+      <c r="BU34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ34" t="n">
         <v>19.5</v>
       </c>
-      <c r="BB34" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>26</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,239 +9230,239 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ham-Kam</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.89</v>
       </c>
-      <c r="G35" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="X35" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF35" t="n">
         <v>4.2</v>
       </c>
-      <c r="L35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG35" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="BH35" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -9499,13 +9499,13 @@
         <v>1000</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="I36" t="n">
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
         <v>1000</v>
@@ -9517,13 +9517,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O36" t="n">
         <v>1.27</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Q36" t="n">
         <v>1.27</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G37" t="n">
         <v>1.42</v>
@@ -9756,7 +9756,7 @@
         <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J37" t="n">
         <v>4.8</v>
@@ -9765,7 +9765,7 @@
         <v>5.7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
@@ -9777,7 +9777,7 @@
         <v>1.28</v>
       </c>
       <c r="P37" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q37" t="n">
         <v>1.84</v>
@@ -9789,7 +9789,7 @@
         <v>3.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U37" t="n">
         <v>1.66</v>
@@ -9873,7 +9873,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV37" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AW37" t="n">
         <v>6.8</v>
@@ -9897,13 +9897,13 @@
         <v>12.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE37" t="n">
         <v>6.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG37" t="n">
         <v>6.8</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>4.4</v>
       </c>
       <c r="H38" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I38" t="n">
         <v>1.9</v>
@@ -10016,7 +10016,7 @@
         <v>4.2</v>
       </c>
       <c r="K38" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10034,19 +10034,19 @@
         <v>2.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="R38" t="n">
         <v>1.68</v>
       </c>
       <c r="S38" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T38" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U38" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V38" t="n">
         <v>2.1</v>
@@ -10061,7 +10061,7 @@
         <v>14.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
         <v>22</v>
@@ -10073,7 +10073,7 @@
         <v>11.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE38" t="n">
         <v>18</v>
@@ -10106,13 +10106,13 @@
         <v>32</v>
       </c>
       <c r="AO38" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AP38" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR38" t="n">
         <v>12.5</v>
@@ -10124,16 +10124,16 @@
         <v>19.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW38" t="n">
         <v>14.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AY38" t="n">
         <v>15</v>
@@ -10145,7 +10145,7 @@
         <v>21</v>
       </c>
       <c r="BB38" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC38" t="n">
         <v>34</v>
@@ -10154,13 +10154,13 @@
         <v>34</v>
       </c>
       <c r="BE38" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF38" t="n">
         <v>21</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G41" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H41" t="n">
         <v>3.25</v>
@@ -10781,22 +10781,22 @@
         <v>3.45</v>
       </c>
       <c r="L41" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O41" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R41" t="n">
         <v>1.24</v>
@@ -10805,10 +10805,10 @@
         <v>4.2</v>
       </c>
       <c r="T41" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U41" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V41" t="n">
         <v>1.34</v>
@@ -10829,10 +10829,10 @@
         <v>80</v>
       </c>
       <c r="AB41" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
         <v>17.5</v>
@@ -10862,16 +10862,16 @@
         <v>60</v>
       </c>
       <c r="AM41" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN41" t="n">
         <v>34</v>
       </c>
       <c r="AO41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP41" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ41" t="n">
         <v>8.6</v>
@@ -10904,31 +10904,31 @@
         <v>15</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC41" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>4.4</v>
       </c>
       <c r="BD41" t="n">
         <v>4.7</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF41" t="n">
         <v>21</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH41" t="n">
         <v>3.1</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ41" t="n">
         <v>11</v>
@@ -10946,13 +10946,13 @@
         <v>5.3</v>
       </c>
       <c r="BO41" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP41" t="n">
         <v>21</v>
       </c>
       <c r="BQ41" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR41" t="n">
         <v>40</v>
@@ -10973,7 +10973,7 @@
         <v>7.8</v>
       </c>
       <c r="BX41" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY41" t="n">
         <v>8.6</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AD Iguatu</t>
+          <t>ABC RN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maguary</t>
+          <t>Aguia de Maraba</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -11803,22 +11803,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O45" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="R45" t="n">
         <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -12024,12 +12024,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Portuguesa RJ</t>
+          <t>AD Iguatu</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EC Sao Jose Porto Alegre</t>
+          <t>Maguary</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12278,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Uberlandia MG</t>
+          <t>Portuguesa RJ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Serra Branca EC</t>
+          <t>EC Sao Jose Porto Alegre</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -12311,22 +12311,22 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
       </c>
       <c r="P47" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R47" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -12532,12 +12532,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Manaura Esporte Clube</t>
+          <t>Uberlandia MG</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Goiatuba EC</t>
+          <t>Serra Branca EC</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -12565,22 +12565,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="O48" t="n">
         <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Q48" t="n">
         <v>1.01</v>
       </c>
       <c r="R48" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S48" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -12786,12 +12786,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ABC RN</t>
+          <t>Manaura Esporte Clube</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aguia de Maraba</t>
+          <t>Goiatuba EC</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -12819,7 +12819,7 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O49" t="n">
         <v>1.01</v>
@@ -12828,13 +12828,13 @@
         <v>1.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R49" t="n">
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
         <v>3.85</v>
       </c>
       <c r="L51" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M51" t="n">
         <v>1.01</v>
@@ -13381,7 +13381,7 @@
         <v>32</v>
       </c>
       <c r="AF51" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AG51" t="n">
         <v>17</v>
@@ -13396,7 +13396,7 @@
         <v>70</v>
       </c>
       <c r="AK51" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL51" t="n">
         <v>55</v>
@@ -13411,58 +13411,58 @@
         <v>24</v>
       </c>
       <c r="AP51" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AQ51" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AR51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG51" t="n">
         <v>3.65</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>3.75</v>
       </c>
       <c r="BH51" t="n">
         <v>3.65</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
         <v>3.1</v>
       </c>
       <c r="K53" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13841,7 +13841,7 @@
         <v>1.45</v>
       </c>
       <c r="P53" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q53" t="n">
         <v>2.34</v>
@@ -13856,7 +13856,7 @@
         <v>1.95</v>
       </c>
       <c r="U53" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V53" t="n">
         <v>1.57</v>
@@ -13868,7 +13868,7 @@
         <v>11.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z53" t="n">
         <v>17</v>
@@ -13901,7 +13901,7 @@
         <v>60</v>
       </c>
       <c r="AJ53" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK53" t="n">
         <v>50</v>
@@ -13928,7 +13928,7 @@
         <v>13.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT53" t="n">
         <v>8.6</v>
@@ -13940,7 +13940,7 @@
         <v>10.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX53" t="n">
         <v>17.5</v>
@@ -13952,25 +13952,25 @@
         <v>17</v>
       </c>
       <c r="BA53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC53" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB53" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>7</v>
-      </c>
       <c r="BD53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH53" t="n">
         <v>1000</v>
@@ -14034,14 +14034,14 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14056,246 +14056,246 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Nacional Potosi</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="G54" t="n">
-        <v>2.5</v>
+        <v>140</v>
       </c>
       <c r="H54" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="I54" t="n">
-        <v>4.6</v>
+        <v>140</v>
       </c>
       <c r="J54" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="K54" t="n">
-        <v>3.45</v>
+        <v>110</v>
       </c>
       <c r="L54" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M54" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="O54" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="P54" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="R54" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S54" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="T54" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U54" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W54" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X54" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y54" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z54" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA54" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB54" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC54" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD54" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE54" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF54" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG54" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH54" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI54" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ54" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK54" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL54" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM54" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO54" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ54" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR54" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV54" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX54" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY54" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AZ54" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC54" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD54" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH54" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BJ54" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK54" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN54" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO54" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP54" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ54" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT54" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU54" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ54" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA54" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14305,251 +14305,251 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="G55" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="H55" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K55" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L55" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M55" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="O55" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="R55" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S55" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX55" t="n">
         <v>4</v>
       </c>
-      <c r="T55" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X55" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>14</v>
-      </c>
       <c r="AY55" t="n">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="AZ55" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB55" t="n">
         <v>4.8</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF55" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE55" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG55" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH55" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ55" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BN55" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BO55" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP55" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT55" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BU55" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV55" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brazilian Serie D</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14559,244 +14559,244 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Capital Clube de Futebol</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nacional AM</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="G56" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H56" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="I56" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J56" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N56" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P56" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="R56" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S56" t="n">
-        <v>1.54</v>
+        <v>4.1</v>
       </c>
       <c r="T56" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U56" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V56" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W56" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH56" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN56" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP56" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT56" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV56" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -14818,12 +14818,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Asa AL</t>
+          <t>Ferroviario</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ivinhema FC</t>
+          <t>Imperatriz MA</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -14833,13 +14833,13 @@
         <v>1000</v>
       </c>
       <c r="H57" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I57" t="n">
         <v>1000</v>
       </c>
       <c r="J57" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K57" t="n">
         <v>1000</v>
@@ -14851,22 +14851,22 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="O57" t="n">
         <v>1.01</v>
       </c>
       <c r="P57" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="R57" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S57" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
@@ -15326,12 +15326,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ferroviario</t>
+          <t>Capital Clube de Futebol</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Imperatriz MA</t>
+          <t>Nacional AM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -15359,22 +15359,22 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O59" t="n">
         <v>1.01</v>
       </c>
       <c r="P59" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="R59" t="n">
         <v>1.18</v>
       </c>
       <c r="S59" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="T59" t="n">
         <v>1.01</v>
@@ -15558,14 +15558,14 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15575,36 +15575,36 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>17:05:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Asa AL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Ivinhema FC</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="G60" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="H60" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="I60" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J60" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K60" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15613,142 +15613,142 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>7</v>
+        <v>1.32</v>
       </c>
       <c r="O60" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>1.32</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="R60" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="S60" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="T60" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="U60" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X60" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z60" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA60" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC60" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD60" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE60" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG60" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH60" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI60" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ60" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK60" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL60" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM60" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO60" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ60" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AR60" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT60" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AU60" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV60" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW60" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AX60" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY60" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ60" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BA60" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB60" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BC60" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD60" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BE60" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF60" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG60" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH60" t="n">
         <v>1000</v>
@@ -15805,21 +15805,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15829,180 +15829,180 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:05:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G61" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H61" t="n">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="I61" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="J61" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="K61" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N61" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P61" t="n">
         <v>3</v>
       </c>
-      <c r="O61" t="n">
+      <c r="Q61" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T61" t="n">
         <v>1.43</v>
       </c>
-      <c r="P61" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S61" t="n">
+      <c r="U61" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X61" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP61" t="n">
         <v>4.1</v>
       </c>
-      <c r="T61" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X61" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC61" t="n">
+      <c r="AQ61" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU61" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV61" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW61" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="AX61" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY61" t="n">
         <v>9</v>
       </c>
       <c r="AZ61" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC61" t="n">
         <v>15</v>
       </c>
-      <c r="BA61" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD61" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BE61" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH61" t="n">
         <v>1000</v>
@@ -16066,14 +16066,14 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Brazilian Serie D</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16088,175 +16088,175 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Guapore RO</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Luverdense</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="G62" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H62" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="I62" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J62" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K62" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
       </c>
       <c r="M62" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R62" t="n">
         <v>1.25</v>
       </c>
-      <c r="O62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S62" t="n">
-        <v>1.43</v>
+        <v>4.2</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V62" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W62" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z62" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA62" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB62" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC62" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD62" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE62" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF62" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG62" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI62" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK62" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL62" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM62" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN62" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO62" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16313,21 +16313,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16337,251 +16337,251 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>Guapore RO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Luverdense</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="G63" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H63" t="n">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="I63" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="K63" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L63" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M63" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="O63" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P63" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.6</v>
+        <v>1.02</v>
       </c>
       <c r="R63" t="n">
         <v>1.18</v>
       </c>
       <c r="S63" t="n">
-        <v>5.3</v>
+        <v>1.43</v>
       </c>
       <c r="T63" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X63" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y63" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z63" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA63" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC63" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD63" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE63" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF63" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG63" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH63" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI63" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ63" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK63" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL63" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM63" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN63" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO63" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ63" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR63" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS63" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT63" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU63" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV63" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW63" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX63" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY63" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ63" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA63" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB63" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC63" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD63" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE63" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF63" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG63" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH63" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI63" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ63" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN63" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP63" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR63" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT63" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV63" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX63" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ63" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA63" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16591,251 +16591,251 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="G64" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H64" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="I64" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J64" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="K64" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L64" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M64" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="O64" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P64" t="n">
-        <v>1.86</v>
+        <v>1.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="R64" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="S64" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="T64" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U64" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="X64" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y64" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z64" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA64" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB64" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC64" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD64" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE64" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF64" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG64" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH64" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI64" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ64" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK64" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL64" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM64" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN64" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO64" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ64" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS64" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT64" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU64" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV64" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW64" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ64" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA64" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD64" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE64" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF64" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG64" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH64" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI64" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ64" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN64" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO64" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP64" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR64" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS64" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT64" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU64" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV64" t="n">
         <v>1000</v>
       </c>
       <c r="BW64" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX64" t="n">
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ64" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA64" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16845,251 +16845,251 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="G65" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="H65" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="I65" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X65" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT65" t="n">
         <v>5.4</v>
       </c>
-      <c r="J65" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K65" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L65" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X65" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC65" t="n">
+      <c r="BU65" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY65" t="n">
         <v>9</v>
       </c>
-      <c r="AD65" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH65" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI65" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ65" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK65" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>26</v>
-      </c>
-      <c r="BT65" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU65" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ65" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA65" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-11 02:42:49</t>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17099,244 +17099,752 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="G66" t="n">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="H66" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="K66" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="L66" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M66" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N66" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="P66" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.48</v>
+        <v>1.99</v>
       </c>
       <c r="R66" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="T66" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U66" t="n">
         <v>2.02</v>
       </c>
-      <c r="U66" t="n">
-        <v>1.79</v>
-      </c>
       <c r="V66" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W66" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="X66" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Y66" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Z66" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AA66" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AB66" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC66" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD66" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE66" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF66" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH66" t="n">
         <v>23</v>
       </c>
       <c r="AI66" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AK66" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AL66" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AM66" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN66" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="AO66" t="n">
         <v>80</v>
       </c>
       <c r="AP66" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT66" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ66" t="n">
+      <c r="AU66" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB66" t="inlineStr">
+        <is>
+          <t>2026-07-11 05:01:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK67" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR66" t="n">
+      <c r="BL67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB67" t="inlineStr">
+        <is>
+          <t>2026-07-11 05:01:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR68" t="n">
         <v>18.5</v>
       </c>
-      <c r="AS66" t="n">
+      <c r="AS68" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB68" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT66" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB66" t="n">
+      <c r="BC68" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>17</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS68" t="n">
         <v>32</v>
       </c>
-      <c r="BC66" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI66" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ66" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN66" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP66" t="n">
+      <c r="BT68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW68" t="n">
         <v>24</v>
       </c>
-      <c r="BQ66" t="n">
-        <v>17</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>32</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU66" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW66" t="n">
-        <v>24</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY66" t="n">
+      <c r="BX68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY68" t="n">
         <v>38</v>
       </c>
-      <c r="BZ66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA66" t="n">
+      <c r="BZ68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA68" t="n">
         <v>34</v>
       </c>
-      <c r="CB66" t="inlineStr">
-        <is>
-          <t>2026-07-11 02:42:49</t>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>2026-07-11 05:01:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB68"/>
+  <dimension ref="A1:CB69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.7</v>
       </c>
       <c r="K2" t="n">
         <v>2.96</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G5" t="n">
         <v>3.2</v>
@@ -1628,13 +1628,13 @@
         <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.47</v>
@@ -1643,7 +1643,7 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.4</v>
@@ -1652,22 +1652,22 @@
         <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
         <v>1.46</v>
@@ -1676,28 +1676,28 @@
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA5" t="n">
         <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
@@ -1712,19 +1712,19 @@
         <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1736,49 +1736,49 @@
         <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
         <v>3.45</v>
@@ -1888,22 +1888,22 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
         <v>2.48</v>
@@ -1924,7 +1924,7 @@
         <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>9.6</v>
@@ -2035,68 +2035,68 @@
         <v>8.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
         <v>2.2</v>
@@ -2175,7 +2175,7 @@
         <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.83</v>
@@ -2241,7 +2241,7 @@
         <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS7" t="n">
         <v>36</v>
@@ -2277,7 +2277,7 @@
         <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
         <v>46</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
         <v>3.05</v>
@@ -2399,7 +2399,7 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -2423,10 +2423,10 @@
         <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
         <v>1.47</v>
@@ -2492,13 +2492,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2522,22 +2522,22 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
         <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
         <v>4.8</v>
@@ -2546,7 +2546,7 @@
         <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
         <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
@@ -2752,7 +2752,7 @@
         <v>17.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT9" t="n">
         <v>7.4</v>
@@ -2764,7 +2764,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2776,25 +2776,25 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC9" t="n">
         <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
         <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
         <v>6.4</v>
@@ -3158,16 +3158,16 @@
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>1.3</v>
@@ -3179,10 +3179,10 @@
         <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.32</v>
+        <v>2.76</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.32</v>
+        <v>3.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.32</v>
+        <v>5.9</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.32</v>
+        <v>5.9</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.32</v>
+        <v>6.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.32</v>
+        <v>6.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.32</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3657,40 +3657,40 @@
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.68</v>
+        <v>1.35</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.16</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="O13" t="n">
         <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>1.96</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -3956,7 +3956,7 @@
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
         <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U16" t="n">
         <v>2.66</v>
@@ -4482,7 +4482,7 @@
         <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>16.5</v>
@@ -4491,10 +4491,10 @@
         <v>44</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
         <v>18.5</v>
@@ -4512,7 +4512,7 @@
         <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
         <v>10</v>
@@ -4527,10 +4527,10 @@
         <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -4542,7 +4542,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
         <v>13.5</v>
@@ -4554,7 +4554,7 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4563,10 +4563,10 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
         <v>9</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN16" t="n">
         <v>5.5</v>
@@ -4602,13 +4602,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
@@ -4620,23 +4620,23 @@
         <v>26</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX16" t="n">
         <v>32</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA16" t="n">
         <v>6.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
         <v>8</v>
@@ -4697,13 +4697,13 @@
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
         <v>1.51</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
         <v>2.28</v>
@@ -4712,7 +4712,7 @@
         <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -4727,7 +4727,7 @@
         <v>36</v>
       </c>
       <c r="Z17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4754,10 +4754,10 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK17" t="n">
         <v>13.5</v>
@@ -4766,7 +4766,7 @@
         <v>29</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
         <v>4.9</v>
@@ -4778,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>32</v>
@@ -4817,7 +4817,7 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BE17" t="n">
         <v>36</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.08</v>
       </c>
       <c r="G18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H18" t="n">
         <v>3.85</v>
@@ -4951,7 +4951,7 @@
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
         <v>1.99</v>
@@ -4972,7 +4972,7 @@
         <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X18" t="n">
         <v>13.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>1.96</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
         <v>4.3</v>
@@ -5193,25 +5193,25 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
         <v>2.68</v>
@@ -5220,7 +5220,7 @@
         <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
@@ -5238,19 +5238,19 @@
         <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
         <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AF19" t="n">
         <v>14</v>
@@ -5262,40 +5262,40 @@
         <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="n">
         <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ19" t="n">
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
@@ -5304,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -5313,7 +5313,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>40</v>
@@ -5328,13 +5328,13 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BF19" t="n">
         <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
         <v>1.14</v>
       </c>
       <c r="S20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5689,13 +5689,13 @@
         <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.54</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K21" t="n">
         <v>5.4</v>
@@ -5713,13 +5713,13 @@
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
         <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S21" t="n">
         <v>2.2</v>
@@ -5767,7 +5767,7 @@
         <v>32</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>32</v>
@@ -5785,13 +5785,13 @@
         <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
@@ -5803,7 +5803,7 @@
         <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
@@ -5815,31 +5815,31 @@
         <v>12.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
         <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
         <v>4.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
         <v>4.7</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5937,166 +5937,166 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9</v>
+        <v>2.98</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
         <v>1.16</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>1.82</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE22" t="n">
         <v>42</v>
       </c>
-      <c r="AD22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>500</v>
-      </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="AO22" t="n">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.52</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.56</v>
+        <v>5.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.58</v>
+        <v>6.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.59</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.51</v>
+        <v>5.7</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.58</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.52</v>
+        <v>5.9</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.49</v>
+        <v>5.3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.53</v>
+        <v>6.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.59</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.57</v>
+        <v>7.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.58</v>
+        <v>7.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>3.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.1</v>
@@ -6224,7 +6224,7 @@
         <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
@@ -6233,7 +6233,7 @@
         <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
         <v>1.96</v>
@@ -6353,68 +6353,68 @@
         <v>5.6</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
@@ -6732,13 +6732,13 @@
         <v>1.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
         <v>2.14</v>
@@ -6747,7 +6747,7 @@
         <v>1.72</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
         <v>2.02</v>
@@ -6861,68 +6861,68 @@
         <v>4.8</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6956,10 +6956,10 @@
         <v>1.44</v>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="H26" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
         <v>1000</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="O26" t="n">
         <v>1.35</v>
@@ -7004,7 +7004,7 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="I27" t="n">
         <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7491,19 +7491,19 @@
         <v>1.33</v>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
         <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U28" t="n">
         <v>2.06</v>
@@ -7518,7 +7518,7 @@
         <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
@@ -7557,7 +7557,7 @@
         <v>22</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
         <v>140</v>
@@ -7575,10 +7575,10 @@
         <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>7.8</v>
@@ -7590,7 +7590,7 @@
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -7602,7 +7602,7 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB28" t="n">
         <v>19.5</v>
@@ -7611,16 +7611,16 @@
         <v>18</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF28" t="n">
         <v>12.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="I29" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
@@ -7745,31 +7745,31 @@
         <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S29" t="n">
         <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U29" t="n">
         <v>2.4</v>
       </c>
       <c r="V29" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y29" t="n">
         <v>12.5</v>
@@ -7781,10 +7781,10 @@
         <v>18.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD29" t="n">
         <v>10.5</v>
@@ -7793,22 +7793,22 @@
         <v>16.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG29" t="n">
         <v>20</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
       </c>
       <c r="AJ29" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL29" t="n">
         <v>55</v>
@@ -7820,7 +7820,7 @@
         <v>44</v>
       </c>
       <c r="AO29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP29" t="n">
         <v>20</v>
@@ -7859,7 +7859,7 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC29" t="n">
         <v>46</v>
@@ -7871,7 +7871,7 @@
         <v>60</v>
       </c>
       <c r="BF29" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
         <v>6.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>1.67</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H30" t="n">
         <v>5.9</v>
@@ -7987,22 +7987,22 @@
         <v>3.85</v>
       </c>
       <c r="L30" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O30" t="n">
         <v>1.45</v>
       </c>
       <c r="P30" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R30" t="n">
         <v>1.22</v>
@@ -8011,16 +8011,16 @@
         <v>4.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V30" t="n">
         <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X30" t="n">
         <v>12.5</v>
@@ -8071,7 +8071,7 @@
         <v>260</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO30" t="n">
         <v>270</v>
@@ -8086,7 +8086,7 @@
         <v>36</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
         <v>4.8</v>
@@ -8119,28 +8119,28 @@
         <v>19</v>
       </c>
       <c r="BD30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF30" t="n">
         <v>12</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="n">
         <v>3</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BJ30" t="n">
         <v>12.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8164,7 +8164,7 @@
         <v>38</v>
       </c>
       <c r="BS30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT30" t="n">
         <v>10</v>
@@ -8188,11 +8188,11 @@
         <v>34</v>
       </c>
       <c r="CA30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>1.69</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I31" t="n">
         <v>6</v>
@@ -8262,7 +8262,7 @@
         <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T31" t="n">
         <v>1.75</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
         <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G33" t="n">
         <v>1.44</v>
@@ -8740,13 +8740,13 @@
         <v>7.8</v>
       </c>
       <c r="I33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
         <v>5.5</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.21</v>
@@ -8755,28 +8755,28 @@
         <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q33" t="n">
         <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
         <v>1.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V33" t="n">
         <v>1.13</v>
@@ -8791,22 +8791,22 @@
         <v>38</v>
       </c>
       <c r="Z33" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD33" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
         <v>11</v>
@@ -8815,64 +8815,64 @@
         <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AI33" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM33" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AO33" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.6</v>
+        <v>48</v>
       </c>
       <c r="AT33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU33" t="n">
         <v>12</v>
       </c>
       <c r="AV33" t="n">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="AX33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="BB33" t="n">
         <v>11.5</v>
@@ -8881,16 +8881,16 @@
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="BH33" t="n">
         <v>4.9</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -9018,13 +9018,13 @@
         <v>2.16</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R34" t="n">
         <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T34" t="n">
         <v>1.69</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O35" t="n">
         <v>1.21</v>
       </c>
       <c r="P35" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q35" t="n">
         <v>1.21</v>
@@ -9323,10 +9323,10 @@
         <v>17</v>
       </c>
       <c r="AH35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI35" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ35" t="n">
         <v>42</v>
@@ -9335,19 +9335,19 @@
         <v>44</v>
       </c>
       <c r="AL35" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM35" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AN35" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO35" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ35" t="n">
         <v>8</v>
@@ -9356,10 +9356,10 @@
         <v>21</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU35" t="n">
         <v>6.2</v>
@@ -9398,7 +9398,7 @@
         <v>4.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
         <v>1.09</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9517,13 +9517,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
         <v>1.27</v>
       </c>
       <c r="P36" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
         <v>1.27</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G37" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="H37" t="n">
         <v>11</v>
@@ -9759,19 +9759,19 @@
         <v>14</v>
       </c>
       <c r="J37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>1.28</v>
@@ -9789,16 +9789,16 @@
         <v>3.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U37" t="n">
         <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="X37" t="n">
         <v>19.5</v>
@@ -9813,7 +9813,7 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC37" t="n">
         <v>14</v>
@@ -9825,10 +9825,10 @@
         <v>280</v>
       </c>
       <c r="AF37" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH37" t="n">
         <v>36</v>
@@ -9840,43 +9840,43 @@
         <v>12.5</v>
       </c>
       <c r="AK37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL37" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM37" t="n">
         <v>270</v>
       </c>
       <c r="AN37" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO37" t="n">
         <v>480</v>
       </c>
       <c r="AP37" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT37" t="n">
         <v>6.2</v>
       </c>
       <c r="AU37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV37" t="n">
         <v>34</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX37" t="n">
         <v>6.4</v>
@@ -9885,10 +9885,10 @@
         <v>9</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB37" t="n">
         <v>9.199999999999999</v>
@@ -9900,19 +9900,19 @@
         <v>38</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF37" t="n">
         <v>6</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH37" t="n">
         <v>3.75</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ37" t="n">
         <v>13.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -10007,100 +10007,100 @@
         <v>4.4</v>
       </c>
       <c r="H38" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J38" t="n">
         <v>4.2</v>
       </c>
       <c r="K38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M38" t="n">
         <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>1.18</v>
       </c>
       <c r="P38" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R38" t="n">
         <v>1.68</v>
       </c>
       <c r="S38" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T38" t="n">
         <v>1.57</v>
       </c>
       <c r="U38" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V38" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W38" t="n">
         <v>1.29</v>
       </c>
       <c r="X38" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Y38" t="n">
         <v>14.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA38" t="n">
         <v>22</v>
       </c>
       <c r="AB38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD38" t="n">
         <v>11</v>
       </c>
       <c r="AE38" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF38" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AG38" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH38" t="n">
         <v>16.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ38" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AL38" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM38" t="n">
-        <v>60</v>
+        <v>790</v>
       </c>
       <c r="AN38" t="n">
         <v>32</v>
@@ -10109,7 +10109,7 @@
         <v>7.8</v>
       </c>
       <c r="AP38" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>12</v>
@@ -10118,7 +10118,7 @@
         <v>12.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT38" t="n">
         <v>19.5</v>
@@ -10133,19 +10133,19 @@
         <v>14.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AY38" t="n">
         <v>15</v>
       </c>
       <c r="AZ38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA38" t="n">
         <v>21</v>
       </c>
       <c r="BB38" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BC38" t="n">
         <v>34</v>
@@ -10154,77 +10154,77 @@
         <v>34</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BF38" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BX38" t="n">
         <v>21</v>
       </c>
-      <c r="BG38" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX38" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -10533,22 +10533,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P40" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="S40" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v>3.25</v>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J41" t="n">
         <v>2.84</v>
@@ -10796,7 +10796,7 @@
         <v>1.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R41" t="n">
         <v>1.24</v>
@@ -10808,10 +10808,10 @@
         <v>1.91</v>
       </c>
       <c r="U41" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V41" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W41" t="n">
         <v>1.62</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -11295,19 +11295,19 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="O43" t="n">
         <v>1.03</v>
       </c>
       <c r="P43" t="n">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="Q43" t="n">
         <v>1.03</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="S43" t="n">
         <v>1.03</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -11803,22 +11803,22 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O45" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P45" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="R45" t="n">
         <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
         <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.22</v>
       </c>
       <c r="G50" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H50" t="n">
         <v>3.05</v>
@@ -13061,7 +13061,7 @@
         <v>3.5</v>
       </c>
       <c r="J50" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K50" t="n">
         <v>4</v>
@@ -13082,13 +13082,13 @@
         <v>2.04</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R50" t="n">
         <v>1.42</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T50" t="n">
         <v>1.67</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="G51" t="n">
         <v>3.55</v>
@@ -13315,13 +13315,13 @@
         <v>2.6</v>
       </c>
       <c r="J51" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
         <v>3.85</v>
       </c>
       <c r="L51" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
         <v>1.01</v>
@@ -13468,7 +13468,7 @@
         <v>3.65</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -13560,16 +13560,16 @@
         <v>2.3</v>
       </c>
       <c r="G52" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I52" t="n">
         <v>3.85</v>
       </c>
       <c r="J52" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K52" t="n">
         <v>3.45</v>
@@ -13581,7 +13581,7 @@
         <v>1.1</v>
       </c>
       <c r="N52" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
         <v>1.46</v>
@@ -13593,7 +13593,7 @@
         <v>2.32</v>
       </c>
       <c r="R52" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S52" t="n">
         <v>4.5</v>
@@ -13608,7 +13608,7 @@
         <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X52" t="n">
         <v>11.5</v>
@@ -13722,7 +13722,7 @@
         <v>2.98</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BJ52" t="n">
         <v>11</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -14034,14 +14034,14 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14056,175 +14056,175 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="G54" t="n">
-        <v>140</v>
+        <v>2.8</v>
       </c>
       <c r="H54" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="I54" t="n">
-        <v>140</v>
+        <v>3.65</v>
       </c>
       <c r="J54" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="K54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X54" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO54" t="n">
         <v>110</v>
       </c>
-      <c r="L54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH54" t="n">
         <v>1000</v>
@@ -14281,21 +14281,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14310,246 +14310,246 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Nacional Potosi</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H55" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J55" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="K55" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L55" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M55" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="O55" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="P55" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="R55" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S55" t="n">
-        <v>3.95</v>
+        <v>1.24</v>
       </c>
       <c r="T55" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U55" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W55" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X55" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z55" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC55" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD55" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE55" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG55" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH55" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI55" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM55" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO55" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV55" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX55" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH55" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BJ55" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK55" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN55" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO55" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP55" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT55" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU55" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ55" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA55" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14559,251 +14559,251 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="G56" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="I56" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K56" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L56" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M56" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="O56" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="R56" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="S56" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T56" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U56" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="V56" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="W56" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="X56" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AA56" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AB56" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC56" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE56" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AF56" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH56" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI56" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AJ56" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AK56" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL56" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM56" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AN56" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO56" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AP56" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="AR56" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="AU56" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV56" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX56" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AY56" t="n">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="AZ56" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB56" t="n">
         <v>4.8</v>
       </c>
       <c r="BC56" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF56" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE56" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG56" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ56" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK56" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BN56" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BO56" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP56" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ56" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT56" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BU56" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV56" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brazilian Serie D</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14813,244 +14813,244 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ferroviario</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Imperatriz MA</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="G57" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H57" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="I57" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J57" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K57" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L57" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M57" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N57" t="n">
-        <v>1.29</v>
+        <v>3.05</v>
       </c>
       <c r="O57" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P57" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="R57" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S57" t="n">
-        <v>1.41</v>
+        <v>4</v>
       </c>
       <c r="T57" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V57" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X57" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y57" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA57" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB57" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC57" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD57" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF57" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG57" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH57" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI57" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL57" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM57" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH57" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI57" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ57" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK57" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN57" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO57" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP57" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ57" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR57" t="n">
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT57" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU57" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV57" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW57" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX57" t="n">
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ57" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -15072,12 +15072,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Treze</t>
+          <t>Ferroviario</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>Imperatriz MA</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -15105,22 +15105,22 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="O58" t="n">
         <v>1.01</v>
       </c>
       <c r="P58" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="R58" t="n">
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -15326,12 +15326,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Capital Clube de Futebol</t>
+          <t>Treze</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nacional AM</t>
+          <t>CRAC</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -15359,7 +15359,7 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="O59" t="n">
         <v>1.01</v>
@@ -15374,7 +15374,7 @@
         <v>1.18</v>
       </c>
       <c r="S59" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="T59" t="n">
         <v>1.01</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
@@ -15580,12 +15580,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Asa AL</t>
+          <t>Capital Clube de Futebol</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ivinhema FC</t>
+          <t>Nacional AM</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -15595,13 +15595,13 @@
         <v>1000</v>
       </c>
       <c r="H60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I60" t="n">
         <v>1000</v>
       </c>
       <c r="J60" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K60" t="n">
         <v>1000</v>
@@ -15613,22 +15613,22 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O60" t="n">
         <v>1.01</v>
       </c>
       <c r="P60" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="R60" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S60" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="T60" t="n">
         <v>1.01</v>
@@ -15812,14 +15812,14 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15829,180 +15829,180 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>17:05:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Asa AL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Ivinhema FC</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="G61" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="H61" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="I61" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J61" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K61" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="O61" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="R61" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="S61" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="T61" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="U61" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X61" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y61" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z61" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA61" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB61" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC61" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD61" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE61" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF61" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG61" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH61" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI61" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ61" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK61" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL61" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM61" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AN61" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO61" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ61" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AR61" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS61" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT61" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV61" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW61" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AX61" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY61" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ61" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BA61" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB61" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC61" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD61" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BE61" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF61" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG61" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH61" t="n">
         <v>1000</v>
@@ -16059,21 +16059,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ61" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16083,251 +16083,251 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:05:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>2.38</v>
       </c>
       <c r="G62" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H62" t="n">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="I62" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="K62" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M62" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N62" t="n">
+        <v>7</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P62" t="n">
         <v>3</v>
       </c>
-      <c r="O62" t="n">
+      <c r="Q62" t="n">
         <v>1.42</v>
       </c>
-      <c r="P62" t="n">
+      <c r="R62" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W62" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q62" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S62" t="n">
+      <c r="X62" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS62" t="n">
         <v>4.2</v>
       </c>
-      <c r="T62" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X62" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP62" t="n">
+      <c r="AT62" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU62" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ62" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV62" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="AX62" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AY62" t="n">
         <v>9</v>
       </c>
       <c r="AZ62" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BB62" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BC62" t="n">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BF62" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH62" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI62" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ62" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK62" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL62" t="n">
         <v>1000</v>
       </c>
       <c r="BM62" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN62" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO62" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP62" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ62" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR62" t="n">
         <v>1000</v>
       </c>
       <c r="BS62" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT62" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU62" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
       </c>
       <c r="BW62" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX62" t="n">
         <v>1000</v>
       </c>
       <c r="BY62" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ62" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA62" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Brazilian Serie D</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16342,175 +16342,175 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Guapore RO</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Luverdense</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="G63" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H63" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="I63" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J63" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K63" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
       </c>
       <c r="M63" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R63" t="n">
         <v>1.25</v>
       </c>
-      <c r="O63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S63" t="n">
-        <v>1.43</v>
+        <v>4.2</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V63" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W63" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X63" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y63" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z63" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA63" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB63" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC63" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD63" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE63" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF63" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG63" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH63" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK63" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL63" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM63" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN63" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO63" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16567,21 +16567,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ63" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16591,33 +16591,33 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Guapore RO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Luverdense</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G64" t="n">
         <v>1000</v>
       </c>
       <c r="H64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I64" t="n">
         <v>1000</v>
       </c>
       <c r="J64" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K64" t="n">
         <v>1000</v>
@@ -16629,22 +16629,22 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O64" t="n">
         <v>1.01</v>
       </c>
       <c r="P64" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R64" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S64" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="T64" t="n">
         <v>1.01</v>
@@ -16713,52 +16713,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16845,251 +16845,251 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="G65" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H65" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>1.09</v>
       </c>
       <c r="K65" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L65" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>2.56</v>
+        <v>1.4</v>
       </c>
       <c r="O65" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="P65" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="R65" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S65" t="n">
-        <v>5.3</v>
+        <v>1.11</v>
       </c>
       <c r="T65" t="n">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="U65" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="W65" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="X65" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y65" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z65" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA65" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB65" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC65" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD65" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE65" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF65" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG65" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH65" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI65" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ65" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK65" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL65" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM65" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN65" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO65" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ65" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR65" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT65" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU65" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV65" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW65" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX65" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY65" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ65" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA65" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB65" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC65" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD65" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF65" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG65" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH65" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI65" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ65" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK65" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN65" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO65" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP65" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ65" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR65" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS65" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT65" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU65" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV65" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX65" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ65" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA65" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17099,251 +17099,251 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="G66" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="H66" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="I66" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="L66" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M66" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="O66" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="P66" t="n">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="R66" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S66" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="T66" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="U66" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="V66" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="W66" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="X66" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX66" t="n">
         <v>16</v>
       </c>
-      <c r="Y66" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>10</v>
-      </c>
       <c r="AY66" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ66" t="n">
         <v>17</v>
       </c>
       <c r="BA66" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB66" t="n">
-        <v>19</v>
+        <v>4.2</v>
       </c>
       <c r="BC66" t="n">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD66" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE66" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BF66" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BG66" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BH66" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="BI66" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="BJ66" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM66" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>13</v>
-      </c>
       <c r="BN66" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO66" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BP66" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BQ66" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BR66" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BS66" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT66" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BU66" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BV66" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW66" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX66" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BZ66" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="CA66" t="n">
         <v>9.4</v>
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -17353,251 +17353,251 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="G67" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H67" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I67" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J67" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L67" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M67" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N67" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="P67" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="R67" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S67" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="T67" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U67" t="n">
         <v>2.02</v>
       </c>
-      <c r="U67" t="n">
-        <v>1.81</v>
-      </c>
       <c r="V67" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W67" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="X67" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Y67" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z67" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA67" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AB67" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC67" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE67" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF67" t="n">
         <v>12.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH67" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI67" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AJ67" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK67" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL67" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AM67" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AN67" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AO67" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF67" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BG67" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BH67" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI67" t="n">
         <v>3.05</v>
       </c>
-      <c r="BI67" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BJ67" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK67" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BL67" t="n">
         <v>1000</v>
       </c>
       <c r="BM67" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN67" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO67" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BQ67" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY67" t="n">
         <v>11</v>
       </c>
-      <c r="BR67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS67" t="n">
+      <c r="BZ67" t="n">
         <v>26</v>
       </c>
-      <c r="BT67" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU67" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ67" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA67" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-07-11 05:01:13</t>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -17607,183 +17607,183 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Confianca</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="G68" t="n">
-        <v>2.76</v>
+        <v>2.02</v>
       </c>
       <c r="H68" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="I68" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K68" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L68" t="n">
         <v>1.49</v>
       </c>
       <c r="M68" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N68" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O68" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="P68" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="R68" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="T68" t="n">
         <v>2.02</v>
       </c>
       <c r="U68" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V68" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="W68" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="X68" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y68" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AA68" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB68" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC68" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD68" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AE68" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF68" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH68" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN68" t="n">
         <v>23</v>
       </c>
-      <c r="AI68" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>42</v>
-      </c>
       <c r="AO68" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AP68" t="n">
-        <v>7.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ68" t="n">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="AR68" t="n">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS68" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AT68" t="n">
-        <v>6.8</v>
+        <v>3.15</v>
       </c>
       <c r="AU68" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AV68" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AW68" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX68" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="AY68" t="n">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="AZ68" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA68" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB68" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC68" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="BD68" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE68" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BF68" t="n">
-        <v>30</v>
+        <v>4.2</v>
       </c>
       <c r="BG68" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BH68" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BI68" t="n">
         <v>2.48</v>
@@ -17792,34 +17792,34 @@
         <v>11.5</v>
       </c>
       <c r="BK68" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BL68" t="n">
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BN68" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BO68" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP68" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BQ68" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BR68" t="n">
         <v>1000</v>
       </c>
       <c r="BS68" t="n">
-        <v>32</v>
+        <v>2.3</v>
       </c>
       <c r="BT68" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU68" t="n">
         <v>4.9</v>
@@ -17828,23 +17828,277 @@
         <v>1000</v>
       </c>
       <c r="BW68" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>2026-07-11 07:19:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC69" t="n">
         <v>24</v>
       </c>
-      <c r="BX68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY68" t="n">
-        <v>38</v>
-      </c>
-      <c r="BZ68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA68" t="n">
-        <v>34</v>
-      </c>
-      <c r="CB68" t="inlineStr">
-        <is>
-          <t>2026-07-11 05:01:13</t>
+      <c r="BD69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>2026-07-11 07:19:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,514 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Club Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-07-12 21:31:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>21:10:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Emelec</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Barcelona (Ecu)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>85</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>80</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>160</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>180</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>140</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>860</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>6</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
